--- a/bantu_migration/data/collected_dates.xlsx
+++ b/bantu_migration/data/collected_dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexe\git-projects\bantu_migration\bantu_migration\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006B6D07-46D0-4688-80D4-4276BBB805F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B587F5C2-0068-478D-B671-558B13905A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2940" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F47665F-9214-4920-A078-13BC87677963}"/>
+    <workbookView xWindow="28680" yWindow="-4920" windowWidth="29040" windowHeight="15720" xr2:uid="{1F47665F-9214-4920-A078-13BC87677963}"/>
   </bookViews>
   <sheets>
     <sheet name="Collected_dates_final" sheetId="5" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Collected_dates_final!$A$1:$U$438</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Collected_dates_working!$A$1:$U$466</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Collected_dates_working!$A$1:$U$480</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8023" uniqueCount="1093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8350" uniqueCount="1136">
   <si>
     <t>Country</t>
   </si>
@@ -3576,9 +3576,6 @@
     <t>de Maret, New Survey of Archaeological Research and Dates for West-Central and North-Central Africa, Journal of African History, 1982</t>
   </si>
   <si>
-    <t>https://www.cambridge.org/core/journals/journal-of-african-history/article/new-survey-of-archaeological-research-and-dates-for-westcentral-and-northcentral-africa/4D3F2150F7CD15ACF5E5E0C7CCEDAE1A</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.cambridge.org/core/journals/journal-of-african-history/article/new-survey-of-archaeological-research-and-dates-for-westcentral-and-northcentral-africa/4D3F2150F7CD15ACF5E5E0C7CCEDAE1A </t>
   </si>
   <si>
@@ -3685,6 +3682,138 @@
   </si>
   <si>
     <t>Manyanga and Chirikure, Archives, Objects, Places and Landscapes : Multidisciplinary Approaches to Decolonised Zimbabwean Pasts, 2017 -- see Chapter 6: Chronology of Early Farming Communities in northern Zimbabwe. Coordinates supplied by Renier van der Merwe, based on Pwiti's 1996 PhD</t>
+  </si>
+  <si>
+    <t>Pta-1633</t>
+  </si>
+  <si>
+    <t>Pta-1747</t>
+  </si>
+  <si>
+    <t>Pta-2160</t>
+  </si>
+  <si>
+    <t>Klingbeil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.jstor.org/stable/3888725 </t>
+  </si>
+  <si>
+    <t>See collation on table 2, page 334, 'Southern African Prehistory and Paleoenvironmnets', Haddon Library</t>
+  </si>
+  <si>
+    <t>Evers, Klingbeil Early Iron Age Sites, Lydenburg, Eastern Transvaal, South Africa, The South African Archaeological Bulletin, 1980</t>
+  </si>
+  <si>
+    <t>The South African Archaeological Bulletin</t>
+  </si>
+  <si>
+    <t>Commando Kop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.jstor.org/stable/3888725  </t>
+  </si>
+  <si>
+    <t>Pta-1817</t>
+  </si>
+  <si>
+    <t>Pta-1957</t>
+  </si>
+  <si>
+    <t>Taba Zika Mambo</t>
+  </si>
+  <si>
+    <t>SR-68</t>
+  </si>
+  <si>
+    <t>SR-512</t>
+  </si>
+  <si>
+    <t>Maggs, The Iron Age south of the Zambezi, in 'Southern African Prehistory and Paleoenvironments', 1984</t>
+  </si>
+  <si>
+    <t>Surtic Farm</t>
+  </si>
+  <si>
+    <t>Pta-1842</t>
+  </si>
+  <si>
+    <t>Sinoia Caves</t>
+  </si>
+  <si>
+    <t>SR-118</t>
+  </si>
+  <si>
+    <t>Thatswane</t>
+  </si>
+  <si>
+    <t>Taukome</t>
+  </si>
+  <si>
+    <t>I-11409</t>
+  </si>
+  <si>
+    <t>I-11415</t>
+  </si>
+  <si>
+    <t>I-11414</t>
+  </si>
+  <si>
+    <t>Pta-1399</t>
+  </si>
+  <si>
+    <t>charcoal and charred bone</t>
+  </si>
+  <si>
+    <t>Berorue Hill</t>
+  </si>
+  <si>
+    <t>Vogel, Pretoria Radiocarbon Dates II, Radiocarbon, 1981</t>
+  </si>
+  <si>
+    <t>https://www.cambridge.org/core/journals/radiocarbon/article/pretoria-radiocarbon-dates-ii/6FCAA5E5E68287EFC9FDF1BC1B8892D6</t>
+  </si>
+  <si>
+    <t>Mathangwane</t>
+  </si>
+  <si>
+    <t>Beta-298612</t>
+  </si>
+  <si>
+    <t>charcoal from grave fill</t>
+  </si>
+  <si>
+    <t>van Waarden, A leopard's kopje burial at Mathangwane in Northeastern Botswana, South African Archaeological Bulletin, 2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://search.informit.org/doi/abs/10.3316/INFORMIT.618866691004462 </t>
+  </si>
+  <si>
+    <t>HAR-1812</t>
+  </si>
+  <si>
+    <t>HAR-1813</t>
+  </si>
+  <si>
+    <t>HAR-1814</t>
+  </si>
+  <si>
+    <t>HAR-1815</t>
+  </si>
+  <si>
+    <t>HAR-1816</t>
+  </si>
+  <si>
+    <t>HAR-1817</t>
+  </si>
+  <si>
+    <t>HAR-1818</t>
+  </si>
+  <si>
+    <t>Manekweni</t>
+  </si>
+  <si>
+    <t>Location from: 'An Investigation of Manekweni, Mozambique', Peter Garlake (Azania, 1976)</t>
   </si>
 </sst>
 </file>
@@ -3802,7 +3931,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
@@ -3825,6 +3954,9 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -4146,7 +4278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A0402B2-C048-4370-AA2B-6532C5727951}">
-  <dimension ref="A1:U442"/>
+  <dimension ref="A1:U463"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -20524,7 +20656,7 @@
         <v>1034</v>
       </c>
       <c r="T408" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="409" spans="1:20" x14ac:dyDescent="0.3">
@@ -20565,7 +20697,7 @@
         <v>1034</v>
       </c>
       <c r="T409" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="410" spans="1:20" x14ac:dyDescent="0.3">
@@ -20606,7 +20738,7 @@
         <v>1034</v>
       </c>
       <c r="T410" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="411" spans="1:20" x14ac:dyDescent="0.3">
@@ -20644,7 +20776,7 @@
         <v>1034</v>
       </c>
       <c r="T411" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="412" spans="1:20" x14ac:dyDescent="0.3">
@@ -20682,7 +20814,7 @@
         <v>1034</v>
       </c>
       <c r="T412" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="413" spans="1:20" x14ac:dyDescent="0.3">
@@ -20717,10 +20849,10 @@
         <v>1056</v>
       </c>
       <c r="S413" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T413" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="414" spans="1:20" x14ac:dyDescent="0.3">
@@ -20755,10 +20887,10 @@
         <v>1056</v>
       </c>
       <c r="S414" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T414" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="415" spans="1:20" x14ac:dyDescent="0.3">
@@ -20793,15 +20925,15 @@
         <v>1056</v>
       </c>
       <c r="S415" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T415" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="416" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B416">
         <v>1665</v>
@@ -20819,7 +20951,7 @@
         <v>38</v>
       </c>
       <c r="M416" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="N416" t="s">
         <v>121</v>
@@ -20834,12 +20966,12 @@
         <v>1034</v>
       </c>
       <c r="T416" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="417" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B417">
         <v>1425</v>
@@ -20857,7 +20989,7 @@
         <v>38</v>
       </c>
       <c r="M417" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="N417" t="s">
         <v>121</v>
@@ -20872,12 +21004,12 @@
         <v>1034</v>
       </c>
       <c r="T417" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="418" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B418">
         <v>1210</v>
@@ -20895,7 +21027,7 @@
         <v>38</v>
       </c>
       <c r="M418" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="N418" t="s">
         <v>121</v>
@@ -20910,12 +21042,12 @@
         <v>1034</v>
       </c>
       <c r="T418" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="419" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B419">
         <v>1285</v>
@@ -20933,7 +21065,7 @@
         <v>38</v>
       </c>
       <c r="M419" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N419" t="s">
         <v>121</v>
@@ -20948,12 +21080,12 @@
         <v>1034</v>
       </c>
       <c r="T419" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="420" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B420">
         <v>1570</v>
@@ -20971,7 +21103,7 @@
         <v>38</v>
       </c>
       <c r="M420" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="N420" t="s">
         <v>121</v>
@@ -20986,12 +21118,12 @@
         <v>1034</v>
       </c>
       <c r="T420" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="421" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B421">
         <v>1695</v>
@@ -21009,7 +21141,7 @@
         <v>38</v>
       </c>
       <c r="M421" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="N421" t="s">
         <v>121</v>
@@ -21024,12 +21156,12 @@
         <v>1034</v>
       </c>
       <c r="T421" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="422" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B422">
         <v>925</v>
@@ -21047,7 +21179,7 @@
         <v>38</v>
       </c>
       <c r="M422" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="N422" t="s">
         <v>121</v>
@@ -21059,15 +21191,15 @@
         <v>1056</v>
       </c>
       <c r="S422" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T422" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="423" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B423">
         <v>1710</v>
@@ -21085,7 +21217,7 @@
         <v>38</v>
       </c>
       <c r="M423" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="N423" t="s">
         <v>121</v>
@@ -21100,12 +21232,12 @@
         <v>1034</v>
       </c>
       <c r="T423" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="424" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B424">
         <v>1730</v>
@@ -21123,7 +21255,7 @@
         <v>38</v>
       </c>
       <c r="M424" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="N424" t="s">
         <v>121</v>
@@ -21138,12 +21270,12 @@
         <v>1034</v>
       </c>
       <c r="T424" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="425" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B425">
         <v>1730</v>
@@ -21161,7 +21293,7 @@
         <v>38</v>
       </c>
       <c r="M425" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="N425" t="s">
         <v>121</v>
@@ -21176,12 +21308,12 @@
         <v>1034</v>
       </c>
       <c r="T425" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="426" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B426">
         <v>1545</v>
@@ -21202,10 +21334,10 @@
         <v>38</v>
       </c>
       <c r="M426" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="N426" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="P426" t="s">
         <v>39</v>
@@ -21217,12 +21349,12 @@
         <v>1034</v>
       </c>
       <c r="T426" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="427" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B427">
         <v>895</v>
@@ -21240,7 +21372,7 @@
         <v>38</v>
       </c>
       <c r="M427" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="N427" t="s">
         <v>121</v>
@@ -21252,15 +21384,15 @@
         <v>1056</v>
       </c>
       <c r="S427" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T427" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="428" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B428">
         <v>1335</v>
@@ -21290,10 +21422,10 @@
         <v>1056</v>
       </c>
       <c r="S428" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T428" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="429" spans="1:20" x14ac:dyDescent="0.3">
@@ -21306,10 +21438,10 @@
       <c r="C429">
         <v>15</v>
       </c>
-      <c r="H429" s="20">
+      <c r="H429">
         <v>30.951000000000001</v>
       </c>
-      <c r="I429" s="20">
+      <c r="I429">
         <v>-16.279</v>
       </c>
       <c r="K429" t="s">
@@ -21347,10 +21479,10 @@
       <c r="C430">
         <v>60</v>
       </c>
-      <c r="H430" s="20">
+      <c r="H430">
         <v>30.951000000000001</v>
       </c>
-      <c r="I430" s="20">
+      <c r="I430">
         <v>-16.279</v>
       </c>
       <c r="K430" t="s">
@@ -21388,10 +21520,10 @@
       <c r="C431">
         <v>150</v>
       </c>
-      <c r="H431" s="20">
+      <c r="H431">
         <v>30.951000000000001</v>
       </c>
-      <c r="I431" s="20">
+      <c r="I431">
         <v>-16.279</v>
       </c>
       <c r="K431" t="s">
@@ -21429,10 +21561,10 @@
       <c r="C432">
         <v>210</v>
       </c>
-      <c r="H432" s="20">
+      <c r="H432">
         <v>30.951000000000001</v>
       </c>
-      <c r="I432" s="20">
+      <c r="I432">
         <v>-16.279</v>
       </c>
       <c r="K432" t="s">
@@ -21470,10 +21602,10 @@
       <c r="C433">
         <v>50</v>
       </c>
-      <c r="H433" s="20">
+      <c r="H433">
         <v>30.826000000000001</v>
       </c>
-      <c r="I433" s="20">
+      <c r="I433">
         <v>-16.277999999999999</v>
       </c>
       <c r="K433" t="s">
@@ -21514,10 +21646,10 @@
       <c r="C434">
         <v>70</v>
       </c>
-      <c r="H434" s="20">
+      <c r="H434">
         <v>30.826000000000001</v>
       </c>
-      <c r="I434" s="20">
+      <c r="I434">
         <v>-16.277999999999999</v>
       </c>
       <c r="K434" t="s">
@@ -21558,10 +21690,10 @@
       <c r="C435">
         <v>50</v>
       </c>
-      <c r="H435" s="20">
+      <c r="H435">
         <v>30.826000000000001</v>
       </c>
-      <c r="I435" s="20">
+      <c r="I435">
         <v>-16.277999999999999</v>
       </c>
       <c r="K435" t="s">
@@ -21602,10 +21734,10 @@
       <c r="C436">
         <v>80</v>
       </c>
-      <c r="H436" s="20">
+      <c r="H436">
         <v>30.826000000000001</v>
       </c>
-      <c r="I436" s="20">
+      <c r="I436">
         <v>-16.277999999999999</v>
       </c>
       <c r="K436" t="s">
@@ -21646,10 +21778,10 @@
       <c r="C437">
         <v>80</v>
       </c>
-      <c r="H437" s="20">
+      <c r="H437">
         <v>30.826000000000001</v>
       </c>
-      <c r="I437" s="20">
+      <c r="I437">
         <v>-16.277999999999999</v>
       </c>
       <c r="K437" t="s">
@@ -21690,10 +21822,10 @@
       <c r="C438">
         <v>70</v>
       </c>
-      <c r="H438" s="20">
+      <c r="H438">
         <v>30.826000000000001</v>
       </c>
-      <c r="I438" s="20">
+      <c r="I438">
         <v>-16.277999999999999</v>
       </c>
       <c r="K438" t="s">
@@ -21734,10 +21866,10 @@
       <c r="C439">
         <v>50</v>
       </c>
-      <c r="H439" s="20">
+      <c r="H439">
         <v>27.610299999999999</v>
       </c>
-      <c r="I439" s="20">
+      <c r="I439">
         <v>-24.290600000000001</v>
       </c>
       <c r="K439" t="s">
@@ -21759,7 +21891,7 @@
         <v>856</v>
       </c>
       <c r="T439" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="440" spans="1:21" x14ac:dyDescent="0.3">
@@ -21772,10 +21904,10 @@
       <c r="C440">
         <v>50</v>
       </c>
-      <c r="H440" s="20">
+      <c r="H440">
         <v>27.610299999999999</v>
       </c>
-      <c r="I440" s="20">
+      <c r="I440">
         <v>-24.290600000000001</v>
       </c>
       <c r="K440" t="s">
@@ -21800,7 +21932,7 @@
         <v>856</v>
       </c>
       <c r="T440" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="441" spans="1:21" x14ac:dyDescent="0.3">
@@ -21813,10 +21945,10 @@
       <c r="C441">
         <v>45</v>
       </c>
-      <c r="H441" s="20">
+      <c r="H441">
         <v>27.610299999999999</v>
       </c>
-      <c r="I441" s="20">
+      <c r="I441">
         <v>-24.290600000000001</v>
       </c>
       <c r="K441" t="s">
@@ -21841,7 +21973,7 @@
         <v>856</v>
       </c>
       <c r="T441" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="442" spans="1:21" x14ac:dyDescent="0.3">
@@ -21854,10 +21986,10 @@
       <c r="C442">
         <v>130</v>
       </c>
-      <c r="H442" s="20">
+      <c r="H442">
         <v>30.951000000000001</v>
       </c>
-      <c r="I442" s="20">
+      <c r="I442">
         <v>-16.279</v>
       </c>
       <c r="K442" t="s">
@@ -21876,13 +22008,781 @@
         <v>435</v>
       </c>
       <c r="R442" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="S442" s="7" t="s">
         <v>462</v>
       </c>
       <c r="T442" s="10" t="s">
         <v>714</v>
+      </c>
+    </row>
+    <row r="443" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B443">
+        <v>1160</v>
+      </c>
+      <c r="C443">
+        <v>50</v>
+      </c>
+      <c r="D443" t="s">
+        <v>25</v>
+      </c>
+      <c r="H443">
+        <v>30.496600000000001</v>
+      </c>
+      <c r="I443">
+        <v>-25.098299999999998</v>
+      </c>
+      <c r="K443" t="s">
+        <v>38</v>
+      </c>
+      <c r="M443" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N443" t="s">
+        <v>156</v>
+      </c>
+      <c r="P443" t="s">
+        <v>39</v>
+      </c>
+      <c r="R443" t="s">
+        <v>1098</v>
+      </c>
+      <c r="S443" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="444" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B444">
+        <v>970</v>
+      </c>
+      <c r="C444">
+        <v>40</v>
+      </c>
+      <c r="D444" t="s">
+        <v>25</v>
+      </c>
+      <c r="H444">
+        <v>30.496600000000001</v>
+      </c>
+      <c r="I444">
+        <v>-25.098299999999998</v>
+      </c>
+      <c r="K444" t="s">
+        <v>38</v>
+      </c>
+      <c r="M444" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N444" t="s">
+        <v>156</v>
+      </c>
+      <c r="P444" t="s">
+        <v>39</v>
+      </c>
+      <c r="R444" t="s">
+        <v>1098</v>
+      </c>
+      <c r="S444" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="445" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B445">
+        <v>1120</v>
+      </c>
+      <c r="C445">
+        <v>50</v>
+      </c>
+      <c r="D445" t="s">
+        <v>25</v>
+      </c>
+      <c r="H445">
+        <v>30.496600000000001</v>
+      </c>
+      <c r="I445">
+        <v>-25.098299999999998</v>
+      </c>
+      <c r="K445" t="s">
+        <v>38</v>
+      </c>
+      <c r="M445" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N445" t="s">
+        <v>156</v>
+      </c>
+      <c r="P445" t="s">
+        <v>39</v>
+      </c>
+      <c r="R445" t="s">
+        <v>1098</v>
+      </c>
+      <c r="S445" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="446" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B446">
+        <v>1115</v>
+      </c>
+      <c r="C446">
+        <v>55</v>
+      </c>
+      <c r="H446">
+        <v>29.18</v>
+      </c>
+      <c r="I446">
+        <v>-22.13</v>
+      </c>
+      <c r="K446" t="s">
+        <v>38</v>
+      </c>
+      <c r="M446" t="s">
+        <v>1100</v>
+      </c>
+      <c r="N446" t="s">
+        <v>488</v>
+      </c>
+      <c r="P446" t="s">
+        <v>39</v>
+      </c>
+      <c r="R446" t="s">
+        <v>780</v>
+      </c>
+      <c r="S446" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="447" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B447">
+        <v>980</v>
+      </c>
+      <c r="C447">
+        <v>40</v>
+      </c>
+      <c r="H447">
+        <v>29.18</v>
+      </c>
+      <c r="I447">
+        <v>-22.13</v>
+      </c>
+      <c r="K447" t="s">
+        <v>38</v>
+      </c>
+      <c r="M447" t="s">
+        <v>1100</v>
+      </c>
+      <c r="N447" t="s">
+        <v>488</v>
+      </c>
+      <c r="P447" t="s">
+        <v>39</v>
+      </c>
+      <c r="R447" t="s">
+        <v>780</v>
+      </c>
+      <c r="S447" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="448" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B448">
+        <v>1080</v>
+      </c>
+      <c r="C448">
+        <v>100</v>
+      </c>
+      <c r="H448">
+        <v>29.06</v>
+      </c>
+      <c r="I448">
+        <v>-19.510000000000002</v>
+      </c>
+      <c r="K448" t="s">
+        <v>38</v>
+      </c>
+      <c r="M448" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N448" t="s">
+        <v>175</v>
+      </c>
+      <c r="P448" t="s">
+        <v>39</v>
+      </c>
+      <c r="R448" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="449" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B449">
+        <v>1210</v>
+      </c>
+      <c r="C449">
+        <v>70</v>
+      </c>
+      <c r="H449">
+        <v>29.06</v>
+      </c>
+      <c r="I449">
+        <v>-19.510000000000002</v>
+      </c>
+      <c r="K449" t="s">
+        <v>38</v>
+      </c>
+      <c r="M449" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N449" t="s">
+        <v>175</v>
+      </c>
+      <c r="P449" t="s">
+        <v>39</v>
+      </c>
+      <c r="R449" t="s">
+        <v>780</v>
+      </c>
+      <c r="S449" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="450" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B450">
+        <v>945</v>
+      </c>
+      <c r="C450">
+        <v>35</v>
+      </c>
+      <c r="H450">
+        <v>31.03</v>
+      </c>
+      <c r="I450">
+        <v>-17.52</v>
+      </c>
+      <c r="K450" t="s">
+        <v>38</v>
+      </c>
+      <c r="M450" t="s">
+        <v>1108</v>
+      </c>
+      <c r="N450" t="s">
+        <v>175</v>
+      </c>
+      <c r="P450" t="s">
+        <v>39</v>
+      </c>
+      <c r="R450" t="s">
+        <v>780</v>
+      </c>
+      <c r="S450" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="451" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B451">
+        <v>1300</v>
+      </c>
+      <c r="C451">
+        <v>95</v>
+      </c>
+      <c r="H451">
+        <v>30.03</v>
+      </c>
+      <c r="I451">
+        <v>-17.329999999999998</v>
+      </c>
+      <c r="K451" t="s">
+        <v>38</v>
+      </c>
+      <c r="M451" t="s">
+        <v>1110</v>
+      </c>
+      <c r="N451" t="s">
+        <v>175</v>
+      </c>
+      <c r="P451" t="s">
+        <v>39</v>
+      </c>
+      <c r="R451" t="s">
+        <v>567</v>
+      </c>
+      <c r="S451" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="452" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B452">
+        <v>1025</v>
+      </c>
+      <c r="C452">
+        <v>80</v>
+      </c>
+      <c r="H452">
+        <v>27.140999999999998</v>
+      </c>
+      <c r="I452">
+        <v>-22.251000000000001</v>
+      </c>
+      <c r="K452" t="s">
+        <v>38</v>
+      </c>
+      <c r="M452" t="s">
+        <v>1112</v>
+      </c>
+      <c r="N452" t="s">
+        <v>488</v>
+      </c>
+      <c r="P452" t="s">
+        <v>39</v>
+      </c>
+      <c r="R452" t="s">
+        <v>1107</v>
+      </c>
+      <c r="S452" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="453" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B453">
+        <v>840</v>
+      </c>
+      <c r="C453">
+        <v>75</v>
+      </c>
+      <c r="H453">
+        <v>27.140999999999998</v>
+      </c>
+      <c r="I453">
+        <v>-22.251000000000001</v>
+      </c>
+      <c r="K453" t="s">
+        <v>38</v>
+      </c>
+      <c r="M453" t="s">
+        <v>1112</v>
+      </c>
+      <c r="N453" t="s">
+        <v>488</v>
+      </c>
+      <c r="P453" t="s">
+        <v>39</v>
+      </c>
+      <c r="R453" t="s">
+        <v>1107</v>
+      </c>
+      <c r="S453" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="454" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B454">
+        <v>995</v>
+      </c>
+      <c r="C454">
+        <v>75</v>
+      </c>
+      <c r="H454">
+        <v>26.94</v>
+      </c>
+      <c r="I454">
+        <v>-22.25</v>
+      </c>
+      <c r="K454" t="s">
+        <v>38</v>
+      </c>
+      <c r="M454" t="s">
+        <v>1113</v>
+      </c>
+      <c r="N454" t="s">
+        <v>488</v>
+      </c>
+      <c r="P454" t="s">
+        <v>39</v>
+      </c>
+      <c r="R454" t="s">
+        <v>1107</v>
+      </c>
+      <c r="S454" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="455" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B455">
+        <v>130</v>
+      </c>
+      <c r="C455">
+        <v>40</v>
+      </c>
+      <c r="D455" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H455">
+        <v>12.33</v>
+      </c>
+      <c r="I455">
+        <v>-16.75</v>
+      </c>
+      <c r="K455" t="s">
+        <v>490</v>
+      </c>
+      <c r="M455" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N455" t="s">
+        <v>50</v>
+      </c>
+      <c r="P455" t="s">
+        <v>39</v>
+      </c>
+      <c r="R455" t="s">
+        <v>1120</v>
+      </c>
+      <c r="S455" s="7" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="456" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B456">
+        <v>920</v>
+      </c>
+      <c r="C456">
+        <v>30</v>
+      </c>
+      <c r="D456" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H456">
+        <v>27.34</v>
+      </c>
+      <c r="I456">
+        <v>-20.99</v>
+      </c>
+      <c r="K456" t="s">
+        <v>38</v>
+      </c>
+      <c r="M456" t="s">
+        <v>1122</v>
+      </c>
+      <c r="N456" t="s">
+        <v>488</v>
+      </c>
+      <c r="P456" t="s">
+        <v>39</v>
+      </c>
+      <c r="R456" s="20" t="s">
+        <v>1125</v>
+      </c>
+      <c r="S456" s="7" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="457" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B457">
+        <v>350</v>
+      </c>
+      <c r="C457">
+        <v>80</v>
+      </c>
+      <c r="H457" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I457" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K457" t="s">
+        <v>38</v>
+      </c>
+      <c r="M457" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N457" t="s">
+        <v>437</v>
+      </c>
+      <c r="P457" t="s">
+        <v>39</v>
+      </c>
+      <c r="R457" t="s">
+        <v>780</v>
+      </c>
+      <c r="S457" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T457" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="458" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B458">
+        <v>410</v>
+      </c>
+      <c r="C458">
+        <v>70</v>
+      </c>
+      <c r="H458" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I458" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K458" t="s">
+        <v>38</v>
+      </c>
+      <c r="M458" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N458" t="s">
+        <v>437</v>
+      </c>
+      <c r="P458" t="s">
+        <v>39</v>
+      </c>
+      <c r="R458" t="s">
+        <v>780</v>
+      </c>
+      <c r="S458" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T458" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="459" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B459">
+        <v>490</v>
+      </c>
+      <c r="C459">
+        <v>70</v>
+      </c>
+      <c r="H459" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I459" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K459" t="s">
+        <v>38</v>
+      </c>
+      <c r="M459" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N459" t="s">
+        <v>437</v>
+      </c>
+      <c r="P459" t="s">
+        <v>39</v>
+      </c>
+      <c r="R459" t="s">
+        <v>780</v>
+      </c>
+      <c r="S459" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T459" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="460" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B460">
+        <v>430</v>
+      </c>
+      <c r="C460">
+        <v>70</v>
+      </c>
+      <c r="H460" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I460" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K460" t="s">
+        <v>38</v>
+      </c>
+      <c r="M460" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N460" t="s">
+        <v>437</v>
+      </c>
+      <c r="P460" t="s">
+        <v>39</v>
+      </c>
+      <c r="R460" t="s">
+        <v>780</v>
+      </c>
+      <c r="S460" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T460" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="461" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B461">
+        <v>570</v>
+      </c>
+      <c r="C461">
+        <v>70</v>
+      </c>
+      <c r="H461" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I461" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K461" t="s">
+        <v>38</v>
+      </c>
+      <c r="M461" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N461" t="s">
+        <v>437</v>
+      </c>
+      <c r="P461" t="s">
+        <v>39</v>
+      </c>
+      <c r="R461" t="s">
+        <v>780</v>
+      </c>
+      <c r="S461" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T461" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="462" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B462">
+        <v>250</v>
+      </c>
+      <c r="C462">
+        <v>70</v>
+      </c>
+      <c r="H462" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I462" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K462" t="s">
+        <v>38</v>
+      </c>
+      <c r="M462" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N462" t="s">
+        <v>437</v>
+      </c>
+      <c r="P462" t="s">
+        <v>39</v>
+      </c>
+      <c r="R462" t="s">
+        <v>780</v>
+      </c>
+      <c r="S462" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T462" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="463" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B463">
+        <v>350</v>
+      </c>
+      <c r="C463">
+        <v>70</v>
+      </c>
+      <c r="H463" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I463" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K463" t="s">
+        <v>38</v>
+      </c>
+      <c r="M463" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N463" t="s">
+        <v>437</v>
+      </c>
+      <c r="P463" t="s">
+        <v>39</v>
+      </c>
+      <c r="R463" t="s">
+        <v>780</v>
+      </c>
+      <c r="S463" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T463" t="s">
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -22246,16 +23146,29 @@
     <hyperlink ref="S440" r:id="rId356" xr:uid="{9EF19F26-8DFE-45B4-BA98-670BAE6879E3}"/>
     <hyperlink ref="S441" r:id="rId357" xr:uid="{9E4FE908-9B6D-4755-BBED-20917B2BBB4D}"/>
     <hyperlink ref="S442" r:id="rId358" xr:uid="{9DA3C36B-D109-45B6-AFCD-B7E142B9B945}"/>
+    <hyperlink ref="S443" r:id="rId359" xr:uid="{0789D77E-B498-4A32-9874-EE4CF82CD265}"/>
+    <hyperlink ref="S451" r:id="rId360" xr:uid="{6A551DA2-803D-4122-8D03-B1669C2A0FA6}"/>
+    <hyperlink ref="S449" r:id="rId361" xr:uid="{C9860BB5-0677-4213-929F-62CF64D58666}"/>
+    <hyperlink ref="S450" r:id="rId362" xr:uid="{F4276AF9-0C4E-450B-A91F-45F6D768ABB5}"/>
+    <hyperlink ref="S446" r:id="rId363" xr:uid="{C6D69A40-3F52-4C05-A3C6-82463D4F8A18}"/>
+    <hyperlink ref="S447" r:id="rId364" xr:uid="{77804A8B-2BCD-41AD-8337-79CD3756C5A9}"/>
+    <hyperlink ref="S456" r:id="rId365" xr:uid="{2F1CA601-46C7-4889-8DBD-DE7BA3AC06FC}"/>
+    <hyperlink ref="S457" r:id="rId366" xr:uid="{0EA5A7B8-C41B-447D-A435-A6CBAECCAB33}"/>
+    <hyperlink ref="S458" r:id="rId367" xr:uid="{795FCDC7-506D-466A-86F9-66B8D7E29DC1}"/>
+    <hyperlink ref="S459" r:id="rId368" xr:uid="{13F35BBC-F388-47B3-A19F-985024994501}"/>
+    <hyperlink ref="S460" r:id="rId369" xr:uid="{071194F3-5C7C-4179-AED8-1CDB7BF0F23E}"/>
+    <hyperlink ref="S461" r:id="rId370" xr:uid="{C1CD83CB-217C-4BE8-A860-4C6020D05816}"/>
+    <hyperlink ref="S462" r:id="rId371" xr:uid="{25BEEB89-8DF7-44F8-B19C-12383A518E30}"/>
+    <hyperlink ref="S463" r:id="rId372" xr:uid="{39AD2BEC-65BE-4185-8DAF-8A098F052626}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId359"/>
+  <pageSetup orientation="portrait" r:id="rId373"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U466"/>
+  <dimension ref="A1:U487"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -22324,7 +23237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -22374,7 +23287,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -22424,7 +23337,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -22474,7 +23387,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -22524,7 +23437,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -22574,7 +23487,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -22624,7 +23537,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -22674,7 +23587,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -22718,7 +23631,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>58</v>
       </c>
@@ -22766,7 +23679,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -22807,7 +23720,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -22848,7 +23761,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
@@ -22896,7 +23809,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -22937,7 +23850,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -22981,7 +23894,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -23025,7 +23938,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>80</v>
       </c>
@@ -23066,7 +23979,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -23107,7 +24020,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -23148,7 +24061,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -23189,7 +24102,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -23233,7 +24146,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -23274,7 +24187,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>103</v>
       </c>
@@ -23315,7 +24228,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>107</v>
       </c>
@@ -23361,7 +24274,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>108</v>
       </c>
@@ -23407,7 +24320,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>109</v>
       </c>
@@ -23453,7 +24366,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>110</v>
       </c>
@@ -23499,7 +24412,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>114</v>
       </c>
@@ -23540,7 +24453,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -23578,7 +24491,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -23616,7 +24529,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -23657,7 +24570,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -23698,7 +24611,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -23736,7 +24649,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -23774,7 +24687,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>129</v>
       </c>
@@ -23812,7 +24725,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -23853,7 +24766,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -23894,7 +24807,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>134</v>
       </c>
@@ -23935,7 +24848,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>135</v>
       </c>
@@ -23976,7 +24889,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>136</v>
       </c>
@@ -24010,7 +24923,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>140</v>
       </c>
@@ -24044,7 +24957,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -24078,7 +24991,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>154</v>
       </c>
@@ -24116,7 +25029,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>386</v>
       </c>
@@ -24157,7 +25070,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>159</v>
       </c>
@@ -24198,7 +25111,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>163</v>
       </c>
@@ -24242,7 +25155,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -24283,7 +25196,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>227</v>
       </c>
@@ -24324,7 +25237,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>172</v>
       </c>
@@ -24655,7 +25568,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>198</v>
       </c>
@@ -24703,7 +25616,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>205</v>
       </c>
@@ -24744,7 +25657,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>211</v>
       </c>
@@ -24785,7 +25698,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>200</v>
       </c>
@@ -24826,7 +25739,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>201</v>
       </c>
@@ -24864,7 +25777,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>202</v>
       </c>
@@ -24902,7 +25815,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>203</v>
       </c>
@@ -24940,7 +25853,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>209</v>
       </c>
@@ -24990,7 +25903,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>210</v>
       </c>
@@ -25038,7 +25951,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>215</v>
       </c>
@@ -25076,7 +25989,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>216</v>
       </c>
@@ -25114,7 +26027,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>217</v>
       </c>
@@ -25155,7 +26068,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>223</v>
       </c>
@@ -25196,7 +26109,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>224</v>
       </c>
@@ -25237,7 +26150,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>343</v>
       </c>
@@ -25281,7 +26194,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>226</v>
       </c>
@@ -25332,7 +26245,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>234</v>
       </c>
@@ -25381,7 +26294,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>230</v>
       </c>
@@ -25430,7 +26343,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>231</v>
       </c>
@@ -25479,7 +26392,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>242</v>
       </c>
@@ -25520,7 +26433,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>244</v>
       </c>
@@ -25559,7 +26472,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>245</v>
       </c>
@@ -25598,7 +26511,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>247</v>
       </c>
@@ -25636,7 +26549,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>248</v>
       </c>
@@ -25674,7 +26587,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>249</v>
       </c>
@@ -25712,7 +26625,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>250</v>
       </c>
@@ -25750,7 +26663,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>251</v>
       </c>
@@ -25788,7 +26701,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>252</v>
       </c>
@@ -25826,7 +26739,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>253</v>
       </c>
@@ -25864,7 +26777,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>254</v>
       </c>
@@ -25902,7 +26815,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -25940,7 +26853,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>257</v>
       </c>
@@ -25978,7 +26891,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>258</v>
       </c>
@@ -26016,7 +26929,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>260</v>
       </c>
@@ -26054,7 +26967,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>263</v>
       </c>
@@ -26095,7 +27008,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>264</v>
       </c>
@@ -26136,7 +27049,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>265</v>
       </c>
@@ -26177,7 +27090,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>268</v>
       </c>
@@ -26218,7 +27131,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>269</v>
       </c>
@@ -26259,7 +27172,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>270</v>
       </c>
@@ -26300,7 +27213,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>271</v>
       </c>
@@ -26338,7 +27251,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>272</v>
       </c>
@@ -26376,7 +27289,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>273</v>
       </c>
@@ -26417,7 +27330,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>274</v>
       </c>
@@ -26458,7 +27371,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>278</v>
       </c>
@@ -26499,7 +27412,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>281</v>
       </c>
@@ -26537,7 +27450,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>282</v>
       </c>
@@ -26575,7 +27488,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>287</v>
       </c>
@@ -26613,7 +27526,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>283</v>
       </c>
@@ -26651,7 +27564,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>284</v>
       </c>
@@ -26689,7 +27602,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>285</v>
       </c>
@@ -26727,7 +27640,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>286</v>
       </c>
@@ -26765,7 +27678,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>287</v>
       </c>
@@ -26803,7 +27716,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>288</v>
       </c>
@@ -26847,7 +27760,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>289</v>
       </c>
@@ -26891,7 +27804,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>292</v>
       </c>
@@ -26935,7 +27848,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>293</v>
       </c>
@@ -26973,7 +27886,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>295</v>
       </c>
@@ -27011,7 +27924,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>296</v>
       </c>
@@ -27049,7 +27962,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>302</v>
       </c>
@@ -27087,7 +28000,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>303</v>
       </c>
@@ -27128,7 +28041,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>304</v>
       </c>
@@ -27167,7 +28080,7 @@
       </c>
       <c r="T118" s="12"/>
     </row>
-    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>307</v>
       </c>
@@ -27208,7 +28121,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>308</v>
       </c>
@@ -27246,7 +28159,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>309</v>
       </c>
@@ -27287,7 +28200,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>310</v>
       </c>
@@ -27328,7 +28241,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>319</v>
       </c>
@@ -27372,7 +28285,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>320</v>
       </c>
@@ -27413,7 +28326,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>326</v>
       </c>
@@ -27577,7 +28490,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>346</v>
       </c>
@@ -27621,7 +28534,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>347</v>
       </c>
@@ -27665,7 +28578,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>348</v>
       </c>
@@ -27709,7 +28622,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>349</v>
       </c>
@@ -27753,7 +28666,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>357</v>
       </c>
@@ -27794,7 +28707,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>358</v>
       </c>
@@ -27835,7 +28748,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>361</v>
       </c>
@@ -27876,7 +28789,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>363</v>
       </c>
@@ -27917,7 +28830,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>367</v>
       </c>
@@ -27958,7 +28871,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>368</v>
       </c>
@@ -27999,7 +28912,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>371</v>
       </c>
@@ -28047,7 +28960,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>372</v>
       </c>
@@ -28088,7 +29001,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" s="16" t="s">
         <v>373</v>
       </c>
@@ -28136,7 +29049,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>374</v>
       </c>
@@ -28177,7 +29090,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" s="16" t="s">
         <v>375</v>
       </c>
@@ -28225,7 +29138,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>376</v>
       </c>
@@ -28266,7 +29179,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" s="16" t="s">
         <v>377</v>
       </c>
@@ -28314,7 +29227,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>378</v>
       </c>
@@ -28355,7 +29268,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>381</v>
       </c>
@@ -28393,7 +29306,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>382</v>
       </c>
@@ -28431,7 +29344,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>383</v>
       </c>
@@ -28469,7 +29382,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>384</v>
       </c>
@@ -28548,7 +29461,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>395</v>
       </c>
@@ -28589,7 +29502,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>406</v>
       </c>
@@ -28630,7 +29543,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>407</v>
       </c>
@@ -28671,7 +29584,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="155" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>408</v>
       </c>
@@ -28712,7 +29625,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="156" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>409</v>
       </c>
@@ -28753,7 +29666,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>410</v>
       </c>
@@ -28794,7 +29707,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>411</v>
       </c>
@@ -28835,7 +29748,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>412</v>
       </c>
@@ -28876,7 +29789,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>413</v>
       </c>
@@ -28917,7 +29830,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>419</v>
       </c>
@@ -28958,7 +29871,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>420</v>
       </c>
@@ -28999,7 +29912,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>421</v>
       </c>
@@ -29040,7 +29953,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>422</v>
       </c>
@@ -29081,7 +29994,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>423</v>
       </c>
@@ -29122,7 +30035,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>424</v>
       </c>
@@ -29163,7 +30076,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>425</v>
       </c>
@@ -29204,7 +30117,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>430</v>
       </c>
@@ -29248,7 +30161,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>432</v>
       </c>
@@ -29289,7 +30202,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>440</v>
       </c>
@@ -29333,7 +30246,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>443</v>
       </c>
@@ -29377,7 +30290,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>448</v>
       </c>
@@ -29421,7 +30334,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>681</v>
       </c>
@@ -29465,7 +30378,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>452</v>
       </c>
@@ -29506,7 +30419,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>455</v>
       </c>
@@ -29557,10 +30470,10 @@
       <c r="C176">
         <v>15</v>
       </c>
-      <c r="H176" s="20">
+      <c r="H176">
         <v>30.951000000000001</v>
       </c>
-      <c r="I176" s="20">
+      <c r="I176">
         <v>-16.279</v>
       </c>
       <c r="K176" t="s">
@@ -29585,7 +30498,7 @@
         <v>462</v>
       </c>
       <c r="T176" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.3">
@@ -29598,10 +30511,10 @@
       <c r="C177">
         <v>60</v>
       </c>
-      <c r="H177" s="20">
+      <c r="H177">
         <v>30.951000000000001</v>
       </c>
-      <c r="I177" s="20">
+      <c r="I177">
         <v>-16.279</v>
       </c>
       <c r="K177" t="s">
@@ -29626,7 +30539,7 @@
         <v>462</v>
       </c>
       <c r="T177" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.3">
@@ -29639,10 +30552,10 @@
       <c r="C178">
         <v>150</v>
       </c>
-      <c r="H178" s="20">
+      <c r="H178">
         <v>30.951000000000001</v>
       </c>
-      <c r="I178" s="20">
+      <c r="I178">
         <v>-16.279</v>
       </c>
       <c r="K178" t="s">
@@ -29667,7 +30580,7 @@
         <v>462</v>
       </c>
       <c r="T178" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.3">
@@ -29680,10 +30593,10 @@
       <c r="C179">
         <v>210</v>
       </c>
-      <c r="H179" s="20">
+      <c r="H179">
         <v>30.951000000000001</v>
       </c>
-      <c r="I179" s="20">
+      <c r="I179">
         <v>-16.279</v>
       </c>
       <c r="K179" t="s">
@@ -29708,7 +30621,7 @@
         <v>462</v>
       </c>
       <c r="T179" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.3">
@@ -29721,10 +30634,10 @@
       <c r="C180">
         <v>50</v>
       </c>
-      <c r="H180" s="20">
+      <c r="H180">
         <v>30.826000000000001</v>
       </c>
-      <c r="I180" s="20">
+      <c r="I180">
         <v>-16.277999999999999</v>
       </c>
       <c r="K180" t="s">
@@ -29765,10 +30678,10 @@
       <c r="C181">
         <v>70</v>
       </c>
-      <c r="H181" s="20">
+      <c r="H181">
         <v>30.826000000000001</v>
       </c>
-      <c r="I181" s="20">
+      <c r="I181">
         <v>-16.277999999999999</v>
       </c>
       <c r="K181" t="s">
@@ -29793,7 +30706,7 @@
         <v>462</v>
       </c>
       <c r="T181" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="U181" t="s">
         <v>478</v>
@@ -29809,10 +30722,10 @@
       <c r="C182">
         <v>50</v>
       </c>
-      <c r="H182" s="20">
+      <c r="H182">
         <v>30.826000000000001</v>
       </c>
-      <c r="I182" s="20">
+      <c r="I182">
         <v>-16.277999999999999</v>
       </c>
       <c r="K182" t="s">
@@ -29837,7 +30750,7 @@
         <v>462</v>
       </c>
       <c r="T182" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="U182" t="s">
         <v>479</v>
@@ -29853,10 +30766,10 @@
       <c r="C183">
         <v>80</v>
       </c>
-      <c r="H183" s="20">
+      <c r="H183">
         <v>30.826000000000001</v>
       </c>
-      <c r="I183" s="20">
+      <c r="I183">
         <v>-16.277999999999999</v>
       </c>
       <c r="K183" t="s">
@@ -29881,7 +30794,7 @@
         <v>462</v>
       </c>
       <c r="T183" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="U183" t="s">
         <v>480</v>
@@ -29897,10 +30810,10 @@
       <c r="C184">
         <v>80</v>
       </c>
-      <c r="H184" s="20">
+      <c r="H184">
         <v>30.826000000000001</v>
       </c>
-      <c r="I184" s="20">
+      <c r="I184">
         <v>-16.277999999999999</v>
       </c>
       <c r="K184" t="s">
@@ -29925,7 +30838,7 @@
         <v>462</v>
       </c>
       <c r="T184" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="U184" t="s">
         <v>481</v>
@@ -29941,10 +30854,10 @@
       <c r="C185">
         <v>70</v>
       </c>
-      <c r="H185" s="20">
+      <c r="H185">
         <v>30.826000000000001</v>
       </c>
-      <c r="I185" s="20">
+      <c r="I185">
         <v>-16.277999999999999</v>
       </c>
       <c r="K185" t="s">
@@ -29969,13 +30882,13 @@
         <v>462</v>
       </c>
       <c r="T185" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="U185" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>487</v>
       </c>
@@ -30016,7 +30929,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>489</v>
       </c>
@@ -30060,7 +30973,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>491</v>
       </c>
@@ -30104,7 +31017,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>492</v>
       </c>
@@ -30148,7 +31061,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A190" s="14" t="s">
         <v>493</v>
       </c>
@@ -30192,7 +31105,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>494</v>
       </c>
@@ -30236,7 +31149,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>495</v>
       </c>
@@ -30280,7 +31193,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>496</v>
       </c>
@@ -30324,7 +31237,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>497</v>
       </c>
@@ -30368,7 +31281,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>498</v>
       </c>
@@ -30412,7 +31325,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>499</v>
       </c>
@@ -30456,7 +31369,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>500</v>
       </c>
@@ -30500,7 +31413,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>501</v>
       </c>
@@ -30544,7 +31457,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>515</v>
       </c>
@@ -30588,7 +31501,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>516</v>
       </c>
@@ -30632,7 +31545,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>517</v>
       </c>
@@ -30676,7 +31589,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>518</v>
       </c>
@@ -30720,7 +31633,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>519</v>
       </c>
@@ -30764,7 +31677,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>540</v>
       </c>
@@ -30808,7 +31721,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>541</v>
       </c>
@@ -30852,7 +31765,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>542</v>
       </c>
@@ -30896,7 +31809,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>548</v>
       </c>
@@ -30937,7 +31850,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>551</v>
       </c>
@@ -30978,7 +31891,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>561</v>
       </c>
@@ -31019,7 +31932,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>552</v>
       </c>
@@ -31060,7 +31973,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>554</v>
       </c>
@@ -31104,7 +32017,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>557</v>
       </c>
@@ -31145,7 +32058,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="213" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>559</v>
       </c>
@@ -31186,7 +32099,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>563</v>
       </c>
@@ -31227,7 +32140,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>589</v>
       </c>
@@ -31271,7 +32184,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>590</v>
       </c>
@@ -31312,7 +32225,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="217" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>572</v>
       </c>
@@ -31350,7 +32263,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="218" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>577</v>
       </c>
@@ -31388,7 +32301,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>579</v>
       </c>
@@ -31426,7 +32339,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>580</v>
       </c>
@@ -31464,7 +32377,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>584</v>
       </c>
@@ -31502,7 +32415,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>585</v>
       </c>
@@ -31540,7 +32453,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>586</v>
       </c>
@@ -31578,7 +32491,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="224" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>587</v>
       </c>
@@ -31616,7 +32529,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="225" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>591</v>
       </c>
@@ -31657,7 +32570,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="226" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>592</v>
       </c>
@@ -31698,7 +32611,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="227" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>593</v>
       </c>
@@ -31739,7 +32652,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="228" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>594</v>
       </c>
@@ -31780,7 +32693,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="229" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>595</v>
       </c>
@@ -31821,7 +32734,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="230" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>596</v>
       </c>
@@ -31862,7 +32775,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="231" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>601</v>
       </c>
@@ -31900,7 +32813,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="232" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>602</v>
       </c>
@@ -31938,7 +32851,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="233" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>603</v>
       </c>
@@ -31976,7 +32889,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="234" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>604</v>
       </c>
@@ -32014,7 +32927,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="235" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>609</v>
       </c>
@@ -32055,7 +32968,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="236" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>608</v>
       </c>
@@ -32093,7 +33006,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="237" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>607</v>
       </c>
@@ -32131,7 +33044,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="238" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>610</v>
       </c>
@@ -32169,7 +33082,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="239" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>611</v>
       </c>
@@ -32207,7 +33120,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="240" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>612</v>
       </c>
@@ -32245,7 +33158,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>613</v>
       </c>
@@ -32283,7 +33196,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>616</v>
       </c>
@@ -32321,7 +33234,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>618</v>
       </c>
@@ -32359,7 +33272,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="244" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>619</v>
       </c>
@@ -32397,7 +33310,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="245" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>621</v>
       </c>
@@ -32435,7 +33348,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="246" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>620</v>
       </c>
@@ -32473,7 +33386,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>623</v>
       </c>
@@ -32508,7 +33421,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="248" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>624</v>
       </c>
@@ -32549,7 +33462,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="249" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>629</v>
       </c>
@@ -32587,7 +33500,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="250" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>630</v>
       </c>
@@ -32625,7 +33538,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>634</v>
       </c>
@@ -32666,7 +33579,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="252" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>635</v>
       </c>
@@ -32707,7 +33620,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="253" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>636</v>
       </c>
@@ -32745,7 +33658,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="254" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>637</v>
       </c>
@@ -32783,7 +33696,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="255" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>337</v>
       </c>
@@ -32821,7 +33734,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="256" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>638</v>
       </c>
@@ -32859,7 +33772,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="257" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>639</v>
       </c>
@@ -32897,7 +33810,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="258" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>640</v>
       </c>
@@ -32935,7 +33848,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="259" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>647</v>
       </c>
@@ -33245,7 +34158,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="267" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>669</v>
       </c>
@@ -33289,7 +34202,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="268" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>673</v>
       </c>
@@ -33330,7 +34243,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="269" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>674</v>
       </c>
@@ -33371,7 +34284,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="270" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>675</v>
       </c>
@@ -33409,7 +34322,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="271" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>676</v>
       </c>
@@ -33447,7 +34360,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="272" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>682</v>
       </c>
@@ -33485,7 +34398,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="273" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>683</v>
       </c>
@@ -33526,7 +34439,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="274" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>684</v>
       </c>
@@ -33564,7 +34477,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="275" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>685</v>
       </c>
@@ -33602,7 +34515,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="276" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>696</v>
       </c>
@@ -33643,7 +34556,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="277" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>693</v>
       </c>
@@ -33684,7 +34597,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="278" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>701</v>
       </c>
@@ -33725,7 +34638,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="279" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>702</v>
       </c>
@@ -33766,7 +34679,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="280" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>703</v>
       </c>
@@ -33807,7 +34720,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="281" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>706</v>
       </c>
@@ -33848,7 +34761,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="282" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>707</v>
       </c>
@@ -33886,7 +34799,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="283" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>708</v>
       </c>
@@ -33924,7 +34837,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="284" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>709</v>
       </c>
@@ -33959,7 +34872,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="285" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>710</v>
       </c>
@@ -33994,7 +34907,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="286" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>711</v>
       </c>
@@ -34029,7 +34942,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="287" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>712</v>
       </c>
@@ -34074,10 +34987,10 @@
       <c r="C288">
         <v>130</v>
       </c>
-      <c r="H288" s="20">
+      <c r="H288">
         <v>30.951000000000001</v>
       </c>
-      <c r="I288" s="20">
+      <c r="I288">
         <v>-16.279</v>
       </c>
       <c r="K288" t="s">
@@ -34096,7 +35009,7 @@
         <v>435</v>
       </c>
       <c r="R288" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="S288" s="7" t="s">
         <v>462</v>
@@ -34105,7 +35018,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>716</v>
       </c>
@@ -34146,7 +35059,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="290" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>717</v>
       </c>
@@ -34190,7 +35103,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="291" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>721</v>
       </c>
@@ -34234,7 +35147,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>722</v>
       </c>
@@ -34278,7 +35191,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>723</v>
       </c>
@@ -34322,7 +35235,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>724</v>
       </c>
@@ -34366,7 +35279,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>727</v>
       </c>
@@ -34404,7 +35317,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>729</v>
       </c>
@@ -34445,7 +35358,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>730</v>
       </c>
@@ -34486,7 +35399,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>734</v>
       </c>
@@ -34530,7 +35443,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>738</v>
       </c>
@@ -34574,7 +35487,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>739</v>
       </c>
@@ -34618,7 +35531,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>740</v>
       </c>
@@ -34659,7 +35572,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>741</v>
       </c>
@@ -34700,7 +35613,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>742</v>
       </c>
@@ -34741,7 +35654,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>743</v>
       </c>
@@ -34820,7 +35733,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="306" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>750</v>
       </c>
@@ -34861,7 +35774,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="307" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>753</v>
       </c>
@@ -34905,7 +35818,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="308" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
         <v>757</v>
       </c>
@@ -34943,7 +35856,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>757</v>
       </c>
@@ -34981,7 +35894,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A310" s="10" t="s">
         <v>757</v>
       </c>
@@ -35019,7 +35932,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="311" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
         <v>757</v>
       </c>
@@ -35057,7 +35970,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="312" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A312" s="10" t="s">
         <v>757</v>
       </c>
@@ -35095,7 +36008,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>766</v>
       </c>
@@ -35133,7 +36046,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="314" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>767</v>
       </c>
@@ -35171,7 +36084,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>768</v>
       </c>
@@ -35209,7 +36122,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="316" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>770</v>
       </c>
@@ -35247,7 +36160,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="317" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>771</v>
       </c>
@@ -35285,7 +36198,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="318" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>778</v>
       </c>
@@ -35326,7 +36239,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="319" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>784</v>
       </c>
@@ -35367,7 +36280,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="320" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>785</v>
       </c>
@@ -35408,7 +36321,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="321" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>790</v>
       </c>
@@ -35446,7 +36359,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="322" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>791</v>
       </c>
@@ -35484,7 +36397,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="323" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>795</v>
       </c>
@@ -35525,7 +36438,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="324" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>798</v>
       </c>
@@ -35563,7 +36476,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="325" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>799</v>
       </c>
@@ -35604,7 +36517,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="326" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>800</v>
       </c>
@@ -35645,7 +36558,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="327" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>803</v>
       </c>
@@ -35686,7 +36599,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="328" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>806</v>
       </c>
@@ -35724,7 +36637,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="329" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>807</v>
       </c>
@@ -35765,7 +36678,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="330" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>808</v>
       </c>
@@ -35806,7 +36719,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="331" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>809</v>
       </c>
@@ -35844,7 +36757,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="332" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>816</v>
       </c>
@@ -35885,7 +36798,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="333" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>817</v>
       </c>
@@ -36233,7 +37146,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="342" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>841</v>
       </c>
@@ -36274,7 +37187,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="343" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>842</v>
       </c>
@@ -36315,7 +37228,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="344" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>843</v>
       </c>
@@ -36356,7 +37269,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="345" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>844</v>
       </c>
@@ -36397,7 +37310,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="346" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>845</v>
       </c>
@@ -36438,7 +37351,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="347" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>851</v>
       </c>
@@ -36448,10 +37361,10 @@
       <c r="C347">
         <v>50</v>
       </c>
-      <c r="H347" s="20">
+      <c r="H347">
         <v>27.610299999999999</v>
       </c>
-      <c r="I347" s="20">
+      <c r="I347">
         <v>-24.290600000000001</v>
       </c>
       <c r="K347" t="s">
@@ -36473,10 +37386,10 @@
         <v>856</v>
       </c>
       <c r="T347" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="348" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="348" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>852</v>
       </c>
@@ -36486,10 +37399,10 @@
       <c r="C348">
         <v>50</v>
       </c>
-      <c r="H348" s="20">
+      <c r="H348">
         <v>27.610299999999999</v>
       </c>
-      <c r="I348" s="20">
+      <c r="I348">
         <v>-24.290600000000001</v>
       </c>
       <c r="K348" t="s">
@@ -36514,10 +37427,10 @@
         <v>856</v>
       </c>
       <c r="T348" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="349" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="349" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>854</v>
       </c>
@@ -36527,10 +37440,10 @@
       <c r="C349">
         <v>45</v>
       </c>
-      <c r="H349" s="20">
+      <c r="H349">
         <v>27.610299999999999</v>
       </c>
-      <c r="I349" s="20">
+      <c r="I349">
         <v>-24.290600000000001</v>
       </c>
       <c r="K349" t="s">
@@ -36555,10 +37468,10 @@
         <v>856</v>
       </c>
       <c r="T349" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="350" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="350" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>860</v>
       </c>
@@ -36593,7 +37506,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="351" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>861</v>
       </c>
@@ -36628,7 +37541,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="352" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>862</v>
       </c>
@@ -36663,7 +37576,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="353" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>863</v>
       </c>
@@ -36698,7 +37611,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="354" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>864</v>
       </c>
@@ -36736,7 +37649,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="355" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>865</v>
       </c>
@@ -36771,7 +37684,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="356" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>866</v>
       </c>
@@ -36809,7 +37722,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="357" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>867</v>
       </c>
@@ -36847,7 +37760,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="358" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>868</v>
       </c>
@@ -36885,7 +37798,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="359" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>907</v>
       </c>
@@ -36923,7 +37836,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="360" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>869</v>
       </c>
@@ -36961,7 +37874,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="361" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>870</v>
       </c>
@@ -36999,7 +37912,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="362" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>872</v>
       </c>
@@ -37043,7 +37956,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="363" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>874</v>
       </c>
@@ -37084,7 +37997,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="364" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>875</v>
       </c>
@@ -37125,7 +38038,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="365" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>876</v>
       </c>
@@ -37169,7 +38082,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="366" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>877</v>
       </c>
@@ -37210,7 +38123,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="367" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>878</v>
       </c>
@@ -37251,7 +38164,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="368" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>879</v>
       </c>
@@ -37292,7 +38205,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="369" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>883</v>
       </c>
@@ -37336,7 +38249,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="370" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>888</v>
       </c>
@@ -37380,7 +38293,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="371" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>895</v>
       </c>
@@ -37424,7 +38337,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="372" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>896</v>
       </c>
@@ -37465,7 +38378,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="373" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>900</v>
       </c>
@@ -37506,7 +38419,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="374" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>903</v>
       </c>
@@ -37702,7 +38615,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="379" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>915</v>
       </c>
@@ -37740,7 +38653,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="380" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>916</v>
       </c>
@@ -37781,7 +38694,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="381" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A381" s="16" t="s">
         <v>917</v>
       </c>
@@ -37827,7 +38740,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="382" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A382" s="16" t="s">
         <v>918</v>
       </c>
@@ -37875,7 +38788,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="383" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>924</v>
       </c>
@@ -37913,7 +38826,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="384" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>925</v>
       </c>
@@ -37951,7 +38864,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="385" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>926</v>
       </c>
@@ -37992,7 +38905,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="386" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>927</v>
       </c>
@@ -38030,7 +38943,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="387" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>929</v>
       </c>
@@ -38071,7 +38984,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="388" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>934</v>
       </c>
@@ -38106,7 +39019,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="389" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>936</v>
       </c>
@@ -38141,7 +39054,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="390" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>937</v>
       </c>
@@ -38176,7 +39089,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="391" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>939</v>
       </c>
@@ -38214,7 +39127,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="392" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>944</v>
       </c>
@@ -38249,7 +39162,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="393" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>945</v>
       </c>
@@ -38287,7 +39200,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="394" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>946</v>
       </c>
@@ -38325,7 +39238,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="395" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>947</v>
       </c>
@@ -38363,7 +39276,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="396" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>948</v>
       </c>
@@ -38401,7 +39314,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="397" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>949</v>
       </c>
@@ -38439,7 +39352,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="398" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>951</v>
       </c>
@@ -38474,7 +39387,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="399" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>954</v>
       </c>
@@ -38512,7 +39425,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="400" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>956</v>
       </c>
@@ -38553,7 +39466,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="401" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>958</v>
       </c>
@@ -38588,7 +39501,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="402" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>960</v>
       </c>
@@ -38626,7 +39539,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="403" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>961</v>
       </c>
@@ -38664,7 +39577,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="404" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>963</v>
       </c>
@@ -38702,7 +39615,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="405" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>965</v>
       </c>
@@ -38737,7 +39650,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="406" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>969</v>
       </c>
@@ -38775,7 +39688,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="407" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>970</v>
       </c>
@@ -38813,7 +39726,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="408" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>971</v>
       </c>
@@ -38851,7 +39764,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="409" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>972</v>
       </c>
@@ -38889,7 +39802,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="410" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>977</v>
       </c>
@@ -38927,7 +39840,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="411" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>978</v>
       </c>
@@ -38965,7 +39878,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="412" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>979</v>
       </c>
@@ -39003,7 +39916,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="413" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>980</v>
       </c>
@@ -39038,7 +39951,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="414" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>981</v>
       </c>
@@ -39073,7 +39986,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="415" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>982</v>
       </c>
@@ -39108,7 +40021,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="416" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>987</v>
       </c>
@@ -39143,7 +40056,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="417" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>990</v>
       </c>
@@ -39178,7 +40091,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="418" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>992</v>
       </c>
@@ -39216,7 +40129,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="419" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>993</v>
       </c>
@@ -39254,7 +40167,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="420" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>998</v>
       </c>
@@ -39292,7 +40205,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="421" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>999</v>
       </c>
@@ -39330,7 +40243,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="422" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1006</v>
       </c>
@@ -39371,7 +40284,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="423" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1007</v>
       </c>
@@ -39412,7 +40325,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="424" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
         <v>1008</v>
       </c>
@@ -39460,7 +40373,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="425" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1009</v>
       </c>
@@ -39501,7 +40414,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="426" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1010</v>
       </c>
@@ -39542,7 +40455,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="427" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1011</v>
       </c>
@@ -39583,7 +40496,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="428" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1012</v>
       </c>
@@ -39624,7 +40537,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="429" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1013</v>
       </c>
@@ -39665,7 +40578,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="430" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1014</v>
       </c>
@@ -39706,7 +40619,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="431" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1015</v>
       </c>
@@ -39747,7 +40660,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="432" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1016</v>
       </c>
@@ -39788,7 +40701,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="433" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1017</v>
       </c>
@@ -39829,7 +40742,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="434" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1018</v>
       </c>
@@ -39870,7 +40783,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="435" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1019</v>
       </c>
@@ -39911,7 +40824,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="436" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1021</v>
       </c>
@@ -39949,7 +40862,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="437" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1022</v>
       </c>
@@ -39987,7 +40900,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="438" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1023</v>
       </c>
@@ -40025,7 +40938,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="439" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1024</v>
       </c>
@@ -40063,7 +40976,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="440" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1025</v>
       </c>
@@ -40101,7 +41014,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="441" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1026</v>
       </c>
@@ -40139,7 +41052,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="442" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1027</v>
       </c>
@@ -40177,7 +41090,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="443" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1028</v>
       </c>
@@ -40215,7 +41128,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="444" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1029</v>
       </c>
@@ -40253,7 +41166,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="445" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1039</v>
       </c>
@@ -40294,7 +41207,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="446" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1047</v>
       </c>
@@ -40332,10 +41245,10 @@
         <v>1034</v>
       </c>
       <c r="T446" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="447" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="447" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1048</v>
       </c>
@@ -40373,10 +41286,10 @@
         <v>1034</v>
       </c>
       <c r="T447" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="448" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="448" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1049</v>
       </c>
@@ -40414,10 +41327,10 @@
         <v>1034</v>
       </c>
       <c r="T448" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="449" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="449" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1051</v>
       </c>
@@ -40452,10 +41365,10 @@
         <v>1034</v>
       </c>
       <c r="T449" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="450" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="450" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1052</v>
       </c>
@@ -40490,10 +41403,10 @@
         <v>1034</v>
       </c>
       <c r="T450" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="451" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="451" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1053</v>
       </c>
@@ -40525,13 +41438,13 @@
         <v>1056</v>
       </c>
       <c r="S451" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T451" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="452" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="452" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1054</v>
       </c>
@@ -40563,13 +41476,13 @@
         <v>1056</v>
       </c>
       <c r="S452" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T452" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="453" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="453" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1055</v>
       </c>
@@ -40601,15 +41514,15 @@
         <v>1056</v>
       </c>
       <c r="S453" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T453" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="454" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="454" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B454">
         <v>1665</v>
@@ -40627,7 +41540,7 @@
         <v>38</v>
       </c>
       <c r="M454" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="N454" t="s">
         <v>121</v>
@@ -40642,12 +41555,12 @@
         <v>1034</v>
       </c>
       <c r="T454" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="455" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="455" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B455">
         <v>1425</v>
@@ -40665,7 +41578,7 @@
         <v>38</v>
       </c>
       <c r="M455" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="N455" t="s">
         <v>121</v>
@@ -40680,12 +41593,12 @@
         <v>1034</v>
       </c>
       <c r="T455" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="456" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="456" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B456">
         <v>1210</v>
@@ -40703,7 +41616,7 @@
         <v>38</v>
       </c>
       <c r="M456" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="N456" t="s">
         <v>121</v>
@@ -40718,12 +41631,12 @@
         <v>1034</v>
       </c>
       <c r="T456" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="457" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="457" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B457">
         <v>1285</v>
@@ -40741,7 +41654,7 @@
         <v>38</v>
       </c>
       <c r="M457" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N457" t="s">
         <v>121</v>
@@ -40756,12 +41669,12 @@
         <v>1034</v>
       </c>
       <c r="T457" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="458" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="458" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B458">
         <v>1570</v>
@@ -40779,7 +41692,7 @@
         <v>38</v>
       </c>
       <c r="M458" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="N458" t="s">
         <v>121</v>
@@ -40794,12 +41707,12 @@
         <v>1034</v>
       </c>
       <c r="T458" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="459" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="459" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B459">
         <v>1695</v>
@@ -40817,7 +41730,7 @@
         <v>38</v>
       </c>
       <c r="M459" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="N459" t="s">
         <v>121</v>
@@ -40832,12 +41745,12 @@
         <v>1034</v>
       </c>
       <c r="T459" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="460" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="460" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B460">
         <v>925</v>
@@ -40855,7 +41768,7 @@
         <v>38</v>
       </c>
       <c r="M460" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="N460" t="s">
         <v>121</v>
@@ -40867,15 +41780,15 @@
         <v>1056</v>
       </c>
       <c r="S460" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T460" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="461" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="461" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B461">
         <v>1710</v>
@@ -40893,7 +41806,7 @@
         <v>38</v>
       </c>
       <c r="M461" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="N461" t="s">
         <v>121</v>
@@ -40908,12 +41821,12 @@
         <v>1034</v>
       </c>
       <c r="T461" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="462" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="462" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B462">
         <v>1730</v>
@@ -40931,7 +41844,7 @@
         <v>38</v>
       </c>
       <c r="M462" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="N462" t="s">
         <v>121</v>
@@ -40946,12 +41859,12 @@
         <v>1034</v>
       </c>
       <c r="T462" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="463" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="463" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B463">
         <v>1730</v>
@@ -40969,7 +41882,7 @@
         <v>38</v>
       </c>
       <c r="M463" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="N463" t="s">
         <v>121</v>
@@ -40984,12 +41897,12 @@
         <v>1034</v>
       </c>
       <c r="T463" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="464" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="464" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B464">
         <v>1545</v>
@@ -41010,10 +41923,10 @@
         <v>38</v>
       </c>
       <c r="M464" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="N464" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="P464" t="s">
         <v>39</v>
@@ -41025,12 +41938,12 @@
         <v>1034</v>
       </c>
       <c r="T464" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="465" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B465">
         <v>895</v>
@@ -41048,7 +41961,7 @@
         <v>38</v>
       </c>
       <c r="M465" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="N465" t="s">
         <v>121</v>
@@ -41060,15 +41973,15 @@
         <v>1056</v>
       </c>
       <c r="S465" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T465" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="466" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B466">
         <v>1335</v>
@@ -41098,20 +42011,782 @@
         <v>1056</v>
       </c>
       <c r="S466" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T466" t="s">
-        <v>1085</v>
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="467" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B467">
+        <v>1160</v>
+      </c>
+      <c r="C467">
+        <v>50</v>
+      </c>
+      <c r="D467" t="s">
+        <v>25</v>
+      </c>
+      <c r="H467">
+        <v>30.496600000000001</v>
+      </c>
+      <c r="I467">
+        <v>-25.098299999999998</v>
+      </c>
+      <c r="K467" t="s">
+        <v>38</v>
+      </c>
+      <c r="M467" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N467" t="s">
+        <v>156</v>
+      </c>
+      <c r="P467" t="s">
+        <v>39</v>
+      </c>
+      <c r="R467" t="s">
+        <v>1098</v>
+      </c>
+      <c r="S467" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="468" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B468">
+        <v>970</v>
+      </c>
+      <c r="C468">
+        <v>40</v>
+      </c>
+      <c r="D468" t="s">
+        <v>25</v>
+      </c>
+      <c r="H468">
+        <v>30.496600000000001</v>
+      </c>
+      <c r="I468">
+        <v>-25.098299999999998</v>
+      </c>
+      <c r="K468" t="s">
+        <v>38</v>
+      </c>
+      <c r="M468" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N468" t="s">
+        <v>156</v>
+      </c>
+      <c r="P468" t="s">
+        <v>39</v>
+      </c>
+      <c r="R468" t="s">
+        <v>1098</v>
+      </c>
+      <c r="S468" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="469" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B469">
+        <v>1120</v>
+      </c>
+      <c r="C469">
+        <v>50</v>
+      </c>
+      <c r="D469" t="s">
+        <v>25</v>
+      </c>
+      <c r="H469">
+        <v>30.496600000000001</v>
+      </c>
+      <c r="I469">
+        <v>-25.098299999999998</v>
+      </c>
+      <c r="K469" t="s">
+        <v>38</v>
+      </c>
+      <c r="M469" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N469" t="s">
+        <v>156</v>
+      </c>
+      <c r="P469" t="s">
+        <v>39</v>
+      </c>
+      <c r="R469" t="s">
+        <v>1098</v>
+      </c>
+      <c r="S469" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="470" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B470">
+        <v>1115</v>
+      </c>
+      <c r="C470">
+        <v>55</v>
+      </c>
+      <c r="H470">
+        <v>29.18</v>
+      </c>
+      <c r="I470">
+        <v>-22.13</v>
+      </c>
+      <c r="K470" t="s">
+        <v>38</v>
+      </c>
+      <c r="M470" t="s">
+        <v>1100</v>
+      </c>
+      <c r="N470" t="s">
+        <v>488</v>
+      </c>
+      <c r="P470" t="s">
+        <v>39</v>
+      </c>
+      <c r="R470" t="s">
+        <v>780</v>
+      </c>
+      <c r="S470" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="471" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B471">
+        <v>980</v>
+      </c>
+      <c r="C471">
+        <v>40</v>
+      </c>
+      <c r="H471">
+        <v>29.18</v>
+      </c>
+      <c r="I471">
+        <v>-22.13</v>
+      </c>
+      <c r="K471" t="s">
+        <v>38</v>
+      </c>
+      <c r="M471" t="s">
+        <v>1100</v>
+      </c>
+      <c r="N471" t="s">
+        <v>488</v>
+      </c>
+      <c r="P471" t="s">
+        <v>39</v>
+      </c>
+      <c r="R471" t="s">
+        <v>780</v>
+      </c>
+      <c r="S471" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="472" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B472">
+        <v>1080</v>
+      </c>
+      <c r="C472">
+        <v>100</v>
+      </c>
+      <c r="H472">
+        <v>29.06</v>
+      </c>
+      <c r="I472">
+        <v>-19.510000000000002</v>
+      </c>
+      <c r="K472" t="s">
+        <v>38</v>
+      </c>
+      <c r="M472" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N472" t="s">
+        <v>175</v>
+      </c>
+      <c r="P472" t="s">
+        <v>39</v>
+      </c>
+      <c r="R472" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="473" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B473">
+        <v>1210</v>
+      </c>
+      <c r="C473">
+        <v>70</v>
+      </c>
+      <c r="H473">
+        <v>29.06</v>
+      </c>
+      <c r="I473">
+        <v>-19.510000000000002</v>
+      </c>
+      <c r="K473" t="s">
+        <v>38</v>
+      </c>
+      <c r="M473" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N473" t="s">
+        <v>175</v>
+      </c>
+      <c r="P473" t="s">
+        <v>39</v>
+      </c>
+      <c r="R473" t="s">
+        <v>780</v>
+      </c>
+      <c r="S473" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="474" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B474">
+        <v>945</v>
+      </c>
+      <c r="C474">
+        <v>35</v>
+      </c>
+      <c r="H474">
+        <v>31.03</v>
+      </c>
+      <c r="I474">
+        <v>-17.52</v>
+      </c>
+      <c r="K474" t="s">
+        <v>38</v>
+      </c>
+      <c r="M474" t="s">
+        <v>1108</v>
+      </c>
+      <c r="N474" t="s">
+        <v>175</v>
+      </c>
+      <c r="P474" t="s">
+        <v>39</v>
+      </c>
+      <c r="R474" t="s">
+        <v>780</v>
+      </c>
+      <c r="S474" s="7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="475" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B475">
+        <v>1300</v>
+      </c>
+      <c r="C475">
+        <v>95</v>
+      </c>
+      <c r="H475">
+        <v>30.03</v>
+      </c>
+      <c r="I475">
+        <v>-17.329999999999998</v>
+      </c>
+      <c r="K475" t="s">
+        <v>38</v>
+      </c>
+      <c r="M475" t="s">
+        <v>1110</v>
+      </c>
+      <c r="N475" t="s">
+        <v>175</v>
+      </c>
+      <c r="P475" t="s">
+        <v>39</v>
+      </c>
+      <c r="R475" t="s">
+        <v>567</v>
+      </c>
+      <c r="S475" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="476" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B476">
+        <v>1025</v>
+      </c>
+      <c r="C476">
+        <v>80</v>
+      </c>
+      <c r="H476">
+        <v>27.140999999999998</v>
+      </c>
+      <c r="I476">
+        <v>-22.251000000000001</v>
+      </c>
+      <c r="K476" t="s">
+        <v>38</v>
+      </c>
+      <c r="M476" t="s">
+        <v>1112</v>
+      </c>
+      <c r="N476" t="s">
+        <v>488</v>
+      </c>
+      <c r="P476" t="s">
+        <v>39</v>
+      </c>
+      <c r="R476" t="s">
+        <v>1107</v>
+      </c>
+      <c r="S476" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="477" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B477">
+        <v>840</v>
+      </c>
+      <c r="C477">
+        <v>75</v>
+      </c>
+      <c r="H477">
+        <v>27.140999999999998</v>
+      </c>
+      <c r="I477">
+        <v>-22.251000000000001</v>
+      </c>
+      <c r="K477" t="s">
+        <v>38</v>
+      </c>
+      <c r="M477" t="s">
+        <v>1112</v>
+      </c>
+      <c r="N477" t="s">
+        <v>488</v>
+      </c>
+      <c r="P477" t="s">
+        <v>39</v>
+      </c>
+      <c r="R477" t="s">
+        <v>1107</v>
+      </c>
+      <c r="S477" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="478" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B478">
+        <v>995</v>
+      </c>
+      <c r="C478">
+        <v>75</v>
+      </c>
+      <c r="H478">
+        <v>26.94</v>
+      </c>
+      <c r="I478">
+        <v>-22.25</v>
+      </c>
+      <c r="K478" t="s">
+        <v>38</v>
+      </c>
+      <c r="M478" t="s">
+        <v>1113</v>
+      </c>
+      <c r="N478" t="s">
+        <v>488</v>
+      </c>
+      <c r="P478" t="s">
+        <v>39</v>
+      </c>
+      <c r="R478" t="s">
+        <v>1107</v>
+      </c>
+      <c r="S478" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="479" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B479">
+        <v>130</v>
+      </c>
+      <c r="C479">
+        <v>40</v>
+      </c>
+      <c r="D479" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H479">
+        <v>12.33</v>
+      </c>
+      <c r="I479">
+        <v>-16.75</v>
+      </c>
+      <c r="K479" t="s">
+        <v>490</v>
+      </c>
+      <c r="M479" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N479" t="s">
+        <v>50</v>
+      </c>
+      <c r="P479" t="s">
+        <v>39</v>
+      </c>
+      <c r="R479" t="s">
+        <v>1120</v>
+      </c>
+      <c r="S479" s="7" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="480" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B480">
+        <v>920</v>
+      </c>
+      <c r="C480">
+        <v>30</v>
+      </c>
+      <c r="D480" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H480">
+        <v>27.34</v>
+      </c>
+      <c r="I480">
+        <v>-20.99</v>
+      </c>
+      <c r="K480" t="s">
+        <v>38</v>
+      </c>
+      <c r="M480" t="s">
+        <v>1122</v>
+      </c>
+      <c r="N480" t="s">
+        <v>488</v>
+      </c>
+      <c r="P480" t="s">
+        <v>39</v>
+      </c>
+      <c r="R480" s="20" t="s">
+        <v>1125</v>
+      </c>
+      <c r="S480" s="7" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="481" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B481">
+        <v>350</v>
+      </c>
+      <c r="C481">
+        <v>80</v>
+      </c>
+      <c r="H481" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I481" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K481" t="s">
+        <v>38</v>
+      </c>
+      <c r="M481" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N481" t="s">
+        <v>437</v>
+      </c>
+      <c r="P481" t="s">
+        <v>39</v>
+      </c>
+      <c r="R481" t="s">
+        <v>780</v>
+      </c>
+      <c r="S481" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T481" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="482" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B482">
+        <v>410</v>
+      </c>
+      <c r="C482">
+        <v>70</v>
+      </c>
+      <c r="H482" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I482" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K482" t="s">
+        <v>38</v>
+      </c>
+      <c r="M482" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N482" t="s">
+        <v>437</v>
+      </c>
+      <c r="P482" t="s">
+        <v>39</v>
+      </c>
+      <c r="R482" t="s">
+        <v>780</v>
+      </c>
+      <c r="S482" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T482" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="483" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B483">
+        <v>490</v>
+      </c>
+      <c r="C483">
+        <v>70</v>
+      </c>
+      <c r="H483" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I483" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K483" t="s">
+        <v>38</v>
+      </c>
+      <c r="M483" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N483" t="s">
+        <v>437</v>
+      </c>
+      <c r="P483" t="s">
+        <v>39</v>
+      </c>
+      <c r="R483" t="s">
+        <v>780</v>
+      </c>
+      <c r="S483" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T483" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="484" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B484">
+        <v>430</v>
+      </c>
+      <c r="C484">
+        <v>70</v>
+      </c>
+      <c r="H484" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I484" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K484" t="s">
+        <v>38</v>
+      </c>
+      <c r="M484" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N484" t="s">
+        <v>437</v>
+      </c>
+      <c r="P484" t="s">
+        <v>39</v>
+      </c>
+      <c r="R484" t="s">
+        <v>780</v>
+      </c>
+      <c r="S484" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T484" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="485" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B485">
+        <v>570</v>
+      </c>
+      <c r="C485">
+        <v>70</v>
+      </c>
+      <c r="H485" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I485" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K485" t="s">
+        <v>38</v>
+      </c>
+      <c r="M485" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N485" t="s">
+        <v>437</v>
+      </c>
+      <c r="P485" t="s">
+        <v>39</v>
+      </c>
+      <c r="R485" t="s">
+        <v>780</v>
+      </c>
+      <c r="S485" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T485" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="486" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B486">
+        <v>250</v>
+      </c>
+      <c r="C486">
+        <v>70</v>
+      </c>
+      <c r="H486" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I486" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K486" t="s">
+        <v>38</v>
+      </c>
+      <c r="M486" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N486" t="s">
+        <v>437</v>
+      </c>
+      <c r="P486" t="s">
+        <v>39</v>
+      </c>
+      <c r="R486" t="s">
+        <v>780</v>
+      </c>
+      <c r="S486" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T486" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="487" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B487">
+        <v>350</v>
+      </c>
+      <c r="C487">
+        <v>70</v>
+      </c>
+      <c r="H487" s="21">
+        <v>34.844999999999999</v>
+      </c>
+      <c r="I487" s="21">
+        <v>-22.184699999999999</v>
+      </c>
+      <c r="K487" t="s">
+        <v>38</v>
+      </c>
+      <c r="M487" t="s">
+        <v>1134</v>
+      </c>
+      <c r="N487" t="s">
+        <v>437</v>
+      </c>
+      <c r="P487" t="s">
+        <v>39</v>
+      </c>
+      <c r="R487" t="s">
+        <v>780</v>
+      </c>
+      <c r="S487" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="T487" t="s">
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U466" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="Zimbabwe"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U480" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="S2" r:id="rId1" xr:uid="{C02C29D8-F2C4-411E-BE0F-C14F29344E0E}"/>
@@ -41496,9 +43171,23 @@
     <hyperlink ref="S464" r:id="rId380" xr:uid="{9FC9DCF5-CF76-44C0-AD70-CB7ED8CD23D6}"/>
     <hyperlink ref="S465" r:id="rId381" xr:uid="{9D343514-E283-4CF4-BAB1-6FFCC9C63355}"/>
     <hyperlink ref="S466" r:id="rId382" xr:uid="{07141425-B2C5-4876-8942-92D11F60257F}"/>
+    <hyperlink ref="S467" r:id="rId383" xr:uid="{839871BD-CB9D-412A-BBAE-C87096B7B273}"/>
+    <hyperlink ref="S475" r:id="rId384" xr:uid="{862E5D85-11C4-4B06-BA10-68411751553A}"/>
+    <hyperlink ref="S473" r:id="rId385" xr:uid="{08F3A868-F854-47A0-AEE6-22216A568297}"/>
+    <hyperlink ref="S474" r:id="rId386" xr:uid="{5C92FA4A-2C52-47D5-B0B7-F5D8FCA99974}"/>
+    <hyperlink ref="S470" r:id="rId387" xr:uid="{D30B4970-A377-4E05-B6FA-28D387F59787}"/>
+    <hyperlink ref="S471" r:id="rId388" xr:uid="{FBF70D17-3383-4A9A-BCFC-31A8E819A587}"/>
+    <hyperlink ref="S480" r:id="rId389" xr:uid="{ED978278-7833-470E-9931-B7A1547D58E0}"/>
+    <hyperlink ref="S481" r:id="rId390" xr:uid="{AF47FA31-679B-4636-B1E4-0ECCD014BC9C}"/>
+    <hyperlink ref="S482" r:id="rId391" xr:uid="{1D6239FC-B588-4BEF-BE3C-94B35ADD7351}"/>
+    <hyperlink ref="S483" r:id="rId392" xr:uid="{B6A04A57-3893-4B19-B91A-A79A8F69AE8E}"/>
+    <hyperlink ref="S484" r:id="rId393" xr:uid="{B63330F8-2347-443B-9220-710BB3D777B3}"/>
+    <hyperlink ref="S485" r:id="rId394" xr:uid="{38CAF884-9F15-4408-93E7-C7A1C6AD12BA}"/>
+    <hyperlink ref="S486" r:id="rId395" xr:uid="{90A9CF1C-DDDE-4B72-8363-7C5A8BC7F43E}"/>
+    <hyperlink ref="S487" r:id="rId396" xr:uid="{8C6BB381-28A8-4A43-A7B9-5F022174757C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId383"/>
+  <pageSetup orientation="portrait" r:id="rId397"/>
 </worksheet>
 </file>
 
@@ -41513,7 +43202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19208A92-499B-437E-AA73-0BB736542043}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="81" bestFit="1" customWidth="1"/>
@@ -41917,7 +43606,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>855</v>
       </c>
@@ -41933,7 +43622,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>882</v>
       </c>
@@ -41941,7 +43630,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>891</v>
       </c>
@@ -41949,7 +43638,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>921</v>
       </c>
@@ -41957,7 +43646,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>931</v>
       </c>
@@ -41965,7 +43654,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>941</v>
       </c>
@@ -41973,7 +43662,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>957</v>
       </c>
@@ -41981,7 +43670,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>967</v>
       </c>
@@ -41989,7 +43678,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>983</v>
       </c>
@@ -41997,7 +43686,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>996</v>
       </c>
@@ -42005,7 +43694,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1003</v>
       </c>
@@ -42013,7 +43702,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1033</v>
       </c>
@@ -42021,7 +43710,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1043</v>
       </c>
@@ -42029,12 +43718,50 @@
         <v>745</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1056</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="7" t="s">
         <v>1057</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B63" t="s">
+        <v>858</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="20" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -42086,6 +43813,9 @@
     <hyperlink ref="B55" r:id="rId44" xr:uid="{E9EF4DCA-91EF-41E3-AF70-3B789FC70AF6}"/>
     <hyperlink ref="B58" r:id="rId45" xr:uid="{CF15D229-9C65-4D95-8D50-8301DDC9BE68}"/>
     <hyperlink ref="B59" r:id="rId46" xr:uid="{B67FA84A-FDE6-4368-AE5D-AE2EB007DBD4}"/>
+    <hyperlink ref="B62" r:id="rId47" xr:uid="{A8E4FB87-F645-48E8-90F3-1A6D870A2788}"/>
+    <hyperlink ref="B61" r:id="rId48" xr:uid="{CDACFC2D-B718-45AE-BD96-F10C2DC7BD16}"/>
+    <hyperlink ref="B65" r:id="rId49" xr:uid="{3F5283A4-BC58-4787-B02F-42E91EC14734}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -42093,7 +43823,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B1FB10-5CDA-4283-82B3-0400FBA4AD78}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -42126,6 +43856,11 @@
         <v>148</v>
       </c>
     </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1099</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bantu_migration/data/collected_dates.xlsx
+++ b/bantu_migration/data/collected_dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexe\git-projects\bantu_migration\bantu_migration\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B587F5C2-0068-478D-B671-558B13905A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9547B0E-0C75-46C4-BC70-C1CF8A86B156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4920" windowWidth="29040" windowHeight="15720" xr2:uid="{1F47665F-9214-4920-A078-13BC87677963}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1F47665F-9214-4920-A078-13BC87677963}"/>
   </bookViews>
   <sheets>
     <sheet name="Collected_dates_final" sheetId="5" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="Journals" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Collected_dates_final!$A$1:$U$438</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Collected_dates_working!$A$1:$U$480</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Collected_dates_final!$A$1:$U$463</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Collected_dates_working!$A$1:$U$487</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8350" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8358" uniqueCount="1137">
   <si>
     <t>Country</t>
   </si>
@@ -3814,6 +3814,9 @@
   </si>
   <si>
     <t>Location from: 'An Investigation of Manekweni, Mozambique', Peter Garlake (Azania, 1976)</t>
+  </si>
+  <si>
+    <t>Site location from google maps</t>
   </si>
 </sst>
 </file>
@@ -3931,7 +3934,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
@@ -3957,7 +3960,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4278,6 +4280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A0402B2-C048-4370-AA2B-6532C5727951}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U463"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4347,7 +4350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -4397,7 +4400,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -4447,7 +4450,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -4497,7 +4500,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -4547,7 +4550,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -4597,7 +4600,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -4647,7 +4650,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -4697,7 +4700,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -4741,7 +4744,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -4782,7 +4785,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -4823,7 +4826,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -4864,7 +4867,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -4908,7 +4911,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>79</v>
       </c>
@@ -4952,7 +4955,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -4993,7 +4996,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -5034,7 +5037,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -5075,7 +5078,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>91</v>
       </c>
@@ -5116,7 +5119,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -5160,7 +5163,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -5201,7 +5204,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>103</v>
       </c>
@@ -5242,7 +5245,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>114</v>
       </c>
@@ -5283,7 +5286,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -5321,7 +5324,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>119</v>
       </c>
@@ -5359,7 +5362,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -5400,7 +5403,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -5441,7 +5444,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>127</v>
       </c>
@@ -5479,7 +5482,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>128</v>
       </c>
@@ -5517,7 +5520,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>129</v>
       </c>
@@ -5555,7 +5558,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>132</v>
       </c>
@@ -5596,7 +5599,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>133</v>
       </c>
@@ -5637,7 +5640,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>134</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>135</v>
       </c>
@@ -5719,7 +5722,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>154</v>
       </c>
@@ -5757,7 +5760,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>386</v>
       </c>
@@ -5798,7 +5801,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>159</v>
       </c>
@@ -5839,7 +5842,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>163</v>
       </c>
@@ -5883,7 +5886,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>169</v>
       </c>
@@ -5924,7 +5927,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>227</v>
       </c>
@@ -5965,7 +5968,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>172</v>
       </c>
@@ -6006,7 +6009,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>177</v>
       </c>
@@ -6047,7 +6050,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>181</v>
       </c>
@@ -6088,7 +6091,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>183</v>
       </c>
@@ -6132,7 +6135,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>186</v>
       </c>
@@ -6176,7 +6179,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>190</v>
       </c>
@@ -6214,7 +6217,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>194</v>
       </c>
@@ -6255,7 +6258,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>195</v>
       </c>
@@ -6296,7 +6299,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>205</v>
       </c>
@@ -6337,7 +6340,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>211</v>
       </c>
@@ -6378,7 +6381,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>200</v>
       </c>
@@ -6419,7 +6422,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>201</v>
       </c>
@@ -6457,7 +6460,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>202</v>
       </c>
@@ -6495,7 +6498,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>203</v>
       </c>
@@ -6533,7 +6536,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>215</v>
       </c>
@@ -6571,7 +6574,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>216</v>
       </c>
@@ -6609,7 +6612,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>217</v>
       </c>
@@ -6650,7 +6653,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>223</v>
       </c>
@@ -6691,7 +6694,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -6732,7 +6735,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>343</v>
       </c>
@@ -6776,7 +6779,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>242</v>
       </c>
@@ -6817,7 +6820,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>244</v>
       </c>
@@ -6856,7 +6859,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>245</v>
       </c>
@@ -6906,10 +6909,10 @@
         <v>90</v>
       </c>
       <c r="H63">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I63">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K63" t="s">
         <v>38</v>
@@ -6931,6 +6934,9 @@
       </c>
       <c r="S63" s="11" t="s">
         <v>240</v>
+      </c>
+      <c r="T63" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
@@ -6944,10 +6950,10 @@
         <v>85</v>
       </c>
       <c r="H64">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I64">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K64" t="s">
         <v>38</v>
@@ -6969,6 +6975,9 @@
       </c>
       <c r="S64" s="11" t="s">
         <v>240</v>
+      </c>
+      <c r="T64" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
@@ -6982,10 +6991,10 @@
         <v>85</v>
       </c>
       <c r="H65">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I65">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K65" t="s">
         <v>38</v>
@@ -7007,6 +7016,9 @@
       </c>
       <c r="S65" s="11" t="s">
         <v>240</v>
+      </c>
+      <c r="T65" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
@@ -7020,10 +7032,10 @@
         <v>60</v>
       </c>
       <c r="H66">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I66">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K66" t="s">
         <v>38</v>
@@ -7045,6 +7057,9 @@
       </c>
       <c r="S66" s="11" t="s">
         <v>240</v>
+      </c>
+      <c r="T66" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.3">
@@ -7058,10 +7073,10 @@
         <v>75</v>
       </c>
       <c r="H67">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I67">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K67" t="s">
         <v>131</v>
@@ -7083,6 +7098,9 @@
       </c>
       <c r="S67" s="11" t="s">
         <v>240</v>
+      </c>
+      <c r="T67" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.3">
@@ -7096,10 +7114,10 @@
         <v>75</v>
       </c>
       <c r="H68">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I68">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K68" t="s">
         <v>131</v>
@@ -7121,6 +7139,9 @@
       </c>
       <c r="S68" s="11" t="s">
         <v>240</v>
+      </c>
+      <c r="T68" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.3">
@@ -7134,10 +7155,10 @@
         <v>80</v>
       </c>
       <c r="H69">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I69">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K69" t="s">
         <v>131</v>
@@ -7159,6 +7180,9 @@
       </c>
       <c r="S69" s="11" t="s">
         <v>240</v>
+      </c>
+      <c r="T69" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.3">
@@ -7172,10 +7196,10 @@
         <v>80</v>
       </c>
       <c r="H70">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I70">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K70" t="s">
         <v>131</v>
@@ -7198,8 +7222,11 @@
       <c r="S70" s="11" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T70" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>256</v>
       </c>
@@ -7237,7 +7264,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>257</v>
       </c>
@@ -7275,7 +7302,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>258</v>
       </c>
@@ -7313,7 +7340,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>260</v>
       </c>
@@ -7351,7 +7378,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>263</v>
       </c>
@@ -7392,7 +7419,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>264</v>
       </c>
@@ -7433,7 +7460,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>265</v>
       </c>
@@ -7474,7 +7501,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>268</v>
       </c>
@@ -7515,7 +7542,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>269</v>
       </c>
@@ -7556,7 +7583,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>270</v>
       </c>
@@ -7597,7 +7624,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>271</v>
       </c>
@@ -7635,7 +7662,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>272</v>
       </c>
@@ -7673,7 +7700,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>273</v>
       </c>
@@ -7714,7 +7741,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>274</v>
       </c>
@@ -7755,7 +7782,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>278</v>
       </c>
@@ -7796,7 +7823,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>281</v>
       </c>
@@ -7834,7 +7861,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>282</v>
       </c>
@@ -7872,7 +7899,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>287</v>
       </c>
@@ -7910,7 +7937,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>283</v>
       </c>
@@ -7948,7 +7975,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>284</v>
       </c>
@@ -7986,7 +8013,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>285</v>
       </c>
@@ -8024,7 +8051,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>286</v>
       </c>
@@ -8062,7 +8089,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>287</v>
       </c>
@@ -8100,7 +8127,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>288</v>
       </c>
@@ -8144,7 +8171,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>289</v>
       </c>
@@ -8188,7 +8215,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>292</v>
       </c>
@@ -8232,7 +8259,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>293</v>
       </c>
@@ -8270,7 +8297,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>295</v>
       </c>
@@ -8308,7 +8335,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>296</v>
       </c>
@@ -8346,7 +8373,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>302</v>
       </c>
@@ -8384,7 +8411,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>303</v>
       </c>
@@ -8425,7 +8452,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>304</v>
       </c>
@@ -8464,7 +8491,7 @@
       </c>
       <c r="T102" s="12"/>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>307</v>
       </c>
@@ -8505,7 +8532,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>308</v>
       </c>
@@ -8543,7 +8570,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>309</v>
       </c>
@@ -8587,7 +8614,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>310</v>
       </c>
@@ -8628,7 +8655,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>319</v>
       </c>
@@ -8672,7 +8699,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>320</v>
       </c>
@@ -8713,7 +8740,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>332</v>
       </c>
@@ -8751,7 +8778,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>333</v>
       </c>
@@ -8789,7 +8816,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>334</v>
       </c>
@@ -8827,7 +8854,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>346</v>
       </c>
@@ -8871,7 +8898,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>347</v>
       </c>
@@ -8915,7 +8942,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>348</v>
       </c>
@@ -8959,7 +8986,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>349</v>
       </c>
@@ -9003,7 +9030,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>357</v>
       </c>
@@ -9044,7 +9071,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>358</v>
       </c>
@@ -9085,7 +9112,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>361</v>
       </c>
@@ -9126,7 +9153,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>363</v>
       </c>
@@ -9167,7 +9194,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>367</v>
       </c>
@@ -9208,7 +9235,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>368</v>
       </c>
@@ -9249,7 +9276,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>372</v>
       </c>
@@ -9290,7 +9317,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>374</v>
       </c>
@@ -9331,7 +9358,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>376</v>
       </c>
@@ -9372,7 +9399,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>378</v>
       </c>
@@ -9413,7 +9440,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>381</v>
       </c>
@@ -9451,7 +9478,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>382</v>
       </c>
@@ -9489,7 +9516,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>383</v>
       </c>
@@ -9527,7 +9554,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>384</v>
       </c>
@@ -9565,7 +9592,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>392</v>
       </c>
@@ -9606,7 +9633,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>395</v>
       </c>
@@ -9647,7 +9674,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>406</v>
       </c>
@@ -9688,7 +9715,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>407</v>
       </c>
@@ -9729,7 +9756,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>408</v>
       </c>
@@ -9770,7 +9797,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>409</v>
       </c>
@@ -9811,7 +9838,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>410</v>
       </c>
@@ -9852,7 +9879,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>411</v>
       </c>
@@ -9893,7 +9920,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>412</v>
       </c>
@@ -9934,7 +9961,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>413</v>
       </c>
@@ -9975,7 +10002,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>419</v>
       </c>
@@ -10016,7 +10043,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>420</v>
       </c>
@@ -10057,7 +10084,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>421</v>
       </c>
@@ -10098,7 +10125,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>422</v>
       </c>
@@ -10139,7 +10166,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>423</v>
       </c>
@@ -10180,7 +10207,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>424</v>
       </c>
@@ -10221,7 +10248,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>425</v>
       </c>
@@ -10262,7 +10289,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>430</v>
       </c>
@@ -10306,7 +10333,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>432</v>
       </c>
@@ -10347,7 +10374,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>440</v>
       </c>
@@ -10391,7 +10418,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>443</v>
       </c>
@@ -10432,7 +10459,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>448</v>
       </c>
@@ -10476,7 +10503,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>681</v>
       </c>
@@ -10520,7 +10547,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>452</v>
       </c>
@@ -10561,7 +10588,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>455</v>
       </c>
@@ -10602,7 +10629,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>487</v>
       </c>
@@ -10643,7 +10670,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>489</v>
       </c>
@@ -10687,7 +10714,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>491</v>
       </c>
@@ -10731,7 +10758,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>492</v>
       </c>
@@ -10775,7 +10802,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="14" t="s">
         <v>493</v>
       </c>
@@ -10819,7 +10846,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>494</v>
       </c>
@@ -10863,7 +10890,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>495</v>
       </c>
@@ -10907,7 +10934,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>496</v>
       </c>
@@ -10951,7 +10978,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>497</v>
       </c>
@@ -10995,7 +11022,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>498</v>
       </c>
@@ -11039,7 +11066,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>499</v>
       </c>
@@ -11083,7 +11110,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>500</v>
       </c>
@@ -11127,7 +11154,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>501</v>
       </c>
@@ -11171,7 +11198,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>515</v>
       </c>
@@ -11215,7 +11242,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>516</v>
       </c>
@@ -11259,7 +11286,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>517</v>
       </c>
@@ -11303,7 +11330,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>518</v>
       </c>
@@ -11347,7 +11374,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>519</v>
       </c>
@@ -11391,7 +11418,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>540</v>
       </c>
@@ -11435,7 +11462,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>541</v>
       </c>
@@ -11479,7 +11506,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>542</v>
       </c>
@@ -11523,7 +11550,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>548</v>
       </c>
@@ -11564,7 +11591,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>551</v>
       </c>
@@ -11605,7 +11632,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>561</v>
       </c>
@@ -11646,7 +11673,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>552</v>
       </c>
@@ -11687,7 +11714,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>554</v>
       </c>
@@ -11731,7 +11758,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>557</v>
       </c>
@@ -11772,7 +11799,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>559</v>
       </c>
@@ -11813,7 +11840,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>563</v>
       </c>
@@ -11854,7 +11881,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>589</v>
       </c>
@@ -11898,7 +11925,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>590</v>
       </c>
@@ -11939,7 +11966,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>572</v>
       </c>
@@ -11977,7 +12004,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>577</v>
       </c>
@@ -12015,7 +12042,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>579</v>
       </c>
@@ -12053,7 +12080,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>580</v>
       </c>
@@ -12091,7 +12118,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>584</v>
       </c>
@@ -12129,7 +12156,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>585</v>
       </c>
@@ -12167,7 +12194,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>586</v>
       </c>
@@ -12205,7 +12232,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>587</v>
       </c>
@@ -12243,7 +12270,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>591</v>
       </c>
@@ -12284,7 +12311,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>592</v>
       </c>
@@ -12325,7 +12352,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>593</v>
       </c>
@@ -12366,7 +12393,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>594</v>
       </c>
@@ -12407,7 +12434,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>595</v>
       </c>
@@ -12448,7 +12475,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>596</v>
       </c>
@@ -12489,7 +12516,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>601</v>
       </c>
@@ -12527,7 +12554,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>602</v>
       </c>
@@ -12565,7 +12592,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>603</v>
       </c>
@@ -12603,7 +12630,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>604</v>
       </c>
@@ -12641,7 +12668,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>609</v>
       </c>
@@ -12682,7 +12709,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>608</v>
       </c>
@@ -12720,7 +12747,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>607</v>
       </c>
@@ -12758,7 +12785,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>610</v>
       </c>
@@ -12796,7 +12823,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>611</v>
       </c>
@@ -12834,7 +12861,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>612</v>
       </c>
@@ -12872,7 +12899,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>613</v>
       </c>
@@ -12910,7 +12937,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>616</v>
       </c>
@@ -12948,7 +12975,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>618</v>
       </c>
@@ -12986,7 +13013,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>619</v>
       </c>
@@ -13024,7 +13051,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>621</v>
       </c>
@@ -13062,7 +13089,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>620</v>
       </c>
@@ -13100,7 +13127,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>623</v>
       </c>
@@ -13135,7 +13162,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>624</v>
       </c>
@@ -13176,7 +13203,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>629</v>
       </c>
@@ -13214,7 +13241,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>630</v>
       </c>
@@ -13252,7 +13279,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>634</v>
       </c>
@@ -13293,7 +13320,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>635</v>
       </c>
@@ -13334,7 +13361,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>636</v>
       </c>
@@ -13372,7 +13399,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>637</v>
       </c>
@@ -13410,7 +13437,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>337</v>
       </c>
@@ -13448,7 +13475,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>638</v>
       </c>
@@ -13486,7 +13513,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>639</v>
       </c>
@@ -13524,7 +13551,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>640</v>
       </c>
@@ -13562,7 +13589,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>647</v>
       </c>
@@ -13606,7 +13633,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>653</v>
       </c>
@@ -13644,7 +13671,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="15" t="s">
         <v>654</v>
       </c>
@@ -13682,7 +13709,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>662</v>
       </c>
@@ -13720,7 +13747,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>663</v>
       </c>
@@ -13758,7 +13785,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>664</v>
       </c>
@@ -13796,7 +13823,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>665</v>
       </c>
@@ -13834,7 +13861,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>666</v>
       </c>
@@ -13872,7 +13899,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>669</v>
       </c>
@@ -13916,7 +13943,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>673</v>
       </c>
@@ -13957,7 +13984,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>674</v>
       </c>
@@ -13998,7 +14025,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>675</v>
       </c>
@@ -14036,7 +14063,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>676</v>
       </c>
@@ -14074,7 +14101,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>682</v>
       </c>
@@ -14112,7 +14139,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>683</v>
       </c>
@@ -14153,7 +14180,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>684</v>
       </c>
@@ -14191,7 +14218,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>685</v>
       </c>
@@ -14229,7 +14256,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>696</v>
       </c>
@@ -14270,7 +14297,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>693</v>
       </c>
@@ -14311,7 +14338,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>701</v>
       </c>
@@ -14352,7 +14379,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>702</v>
       </c>
@@ -14393,7 +14420,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>703</v>
       </c>
@@ -14434,7 +14461,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>706</v>
       </c>
@@ -14475,7 +14502,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>707</v>
       </c>
@@ -14513,7 +14540,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>708</v>
       </c>
@@ -14551,7 +14578,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>709</v>
       </c>
@@ -14586,7 +14613,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>710</v>
       </c>
@@ -14621,7 +14648,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>711</v>
       </c>
@@ -14656,7 +14683,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>712</v>
       </c>
@@ -14691,7 +14718,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>716</v>
       </c>
@@ -14732,7 +14759,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>717</v>
       </c>
@@ -14776,7 +14803,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>721</v>
       </c>
@@ -14820,7 +14847,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>722</v>
       </c>
@@ -14864,7 +14891,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>723</v>
       </c>
@@ -14908,7 +14935,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>724</v>
       </c>
@@ -14952,7 +14979,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>727</v>
       </c>
@@ -14990,7 +15017,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>729</v>
       </c>
@@ -15031,7 +15058,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>730</v>
       </c>
@@ -15072,7 +15099,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>734</v>
       </c>
@@ -15116,7 +15143,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>738</v>
       </c>
@@ -15160,7 +15187,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>739</v>
       </c>
@@ -15204,7 +15231,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>740</v>
       </c>
@@ -15245,7 +15272,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>741</v>
       </c>
@@ -15286,7 +15313,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>742</v>
       </c>
@@ -15327,7 +15354,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>743</v>
       </c>
@@ -15368,7 +15395,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>747</v>
       </c>
@@ -15406,7 +15433,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>750</v>
       </c>
@@ -15447,7 +15474,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>753</v>
       </c>
@@ -15491,7 +15518,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="10" t="s">
         <v>757</v>
       </c>
@@ -15529,7 +15556,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="10" t="s">
         <v>757</v>
       </c>
@@ -15567,7 +15594,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="10" t="s">
         <v>757</v>
       </c>
@@ -15605,7 +15632,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="10" t="s">
         <v>757</v>
       </c>
@@ -15643,7 +15670,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="10" t="s">
         <v>757</v>
       </c>
@@ -15681,7 +15708,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>766</v>
       </c>
@@ -15719,7 +15746,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>767</v>
       </c>
@@ -15757,7 +15784,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>768</v>
       </c>
@@ -15795,7 +15822,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>770</v>
       </c>
@@ -15833,7 +15860,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>771</v>
       </c>
@@ -15871,7 +15898,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>778</v>
       </c>
@@ -15912,7 +15939,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>784</v>
       </c>
@@ -15953,7 +15980,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>785</v>
       </c>
@@ -15994,7 +16021,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>790</v>
       </c>
@@ -16032,7 +16059,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>791</v>
       </c>
@@ -16070,7 +16097,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>795</v>
       </c>
@@ -16111,7 +16138,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>798</v>
       </c>
@@ -16149,7 +16176,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>799</v>
       </c>
@@ -16190,7 +16217,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>800</v>
       </c>
@@ -16231,7 +16258,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>803</v>
       </c>
@@ -16272,7 +16299,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>806</v>
       </c>
@@ -16310,7 +16337,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>807</v>
       </c>
@@ -16351,7 +16378,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>808</v>
       </c>
@@ -16392,7 +16419,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>809</v>
       </c>
@@ -16430,7 +16457,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>816</v>
       </c>
@@ -16471,7 +16498,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>817</v>
       </c>
@@ -16512,7 +16539,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>822</v>
       </c>
@@ -16550,7 +16577,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>823</v>
       </c>
@@ -16588,7 +16615,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>824</v>
       </c>
@@ -16626,7 +16653,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>825</v>
       </c>
@@ -16664,7 +16691,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>826</v>
       </c>
@@ -16702,7 +16729,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>835</v>
       </c>
@@ -16743,7 +16770,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>836</v>
       </c>
@@ -16781,7 +16808,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>837</v>
       </c>
@@ -16819,7 +16846,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>841</v>
       </c>
@@ -16860,7 +16887,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>842</v>
       </c>
@@ -16901,7 +16928,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>843</v>
       </c>
@@ -16942,7 +16969,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>844</v>
       </c>
@@ -16983,7 +17010,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>845</v>
       </c>
@@ -17024,7 +17051,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>860</v>
       </c>
@@ -17059,7 +17086,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>861</v>
       </c>
@@ -17094,7 +17121,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>862</v>
       </c>
@@ -17129,7 +17156,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>863</v>
       </c>
@@ -17164,7 +17191,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>864</v>
       </c>
@@ -17202,7 +17229,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>865</v>
       </c>
@@ -17237,7 +17264,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>866</v>
       </c>
@@ -17275,7 +17302,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>867</v>
       </c>
@@ -17313,7 +17340,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>868</v>
       </c>
@@ -17351,7 +17378,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>907</v>
       </c>
@@ -17389,7 +17416,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>869</v>
       </c>
@@ -17427,7 +17454,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>870</v>
       </c>
@@ -17465,7 +17492,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>872</v>
       </c>
@@ -17509,7 +17536,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>874</v>
       </c>
@@ -17550,7 +17577,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>875</v>
       </c>
@@ -17591,7 +17618,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>876</v>
       </c>
@@ -17635,7 +17662,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>877</v>
       </c>
@@ -17676,7 +17703,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>878</v>
       </c>
@@ -17717,7 +17744,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>879</v>
       </c>
@@ -17758,7 +17785,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>883</v>
       </c>
@@ -17802,7 +17829,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>888</v>
       </c>
@@ -17846,7 +17873,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>895</v>
       </c>
@@ -17890,7 +17917,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>896</v>
       </c>
@@ -17931,7 +17958,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>900</v>
       </c>
@@ -17972,7 +17999,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>903</v>
       </c>
@@ -18010,7 +18037,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>904</v>
       </c>
@@ -18051,7 +18078,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>910</v>
       </c>
@@ -18092,7 +18119,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>911</v>
       </c>
@@ -18130,7 +18157,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>912</v>
       </c>
@@ -18168,7 +18195,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>915</v>
       </c>
@@ -18206,7 +18233,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>916</v>
       </c>
@@ -18247,7 +18274,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>924</v>
       </c>
@@ -18285,7 +18312,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>925</v>
       </c>
@@ -18323,7 +18350,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>926</v>
       </c>
@@ -18364,7 +18391,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>927</v>
       </c>
@@ -18402,7 +18429,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>929</v>
       </c>
@@ -18443,7 +18470,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>934</v>
       </c>
@@ -18478,7 +18505,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>936</v>
       </c>
@@ -18513,7 +18540,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>937</v>
       </c>
@@ -18548,7 +18575,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>939</v>
       </c>
@@ -18586,7 +18613,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>944</v>
       </c>
@@ -18621,7 +18648,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>945</v>
       </c>
@@ -18659,7 +18686,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>946</v>
       </c>
@@ -18697,7 +18724,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>947</v>
       </c>
@@ -18735,7 +18762,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>948</v>
       </c>
@@ -18773,7 +18800,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>949</v>
       </c>
@@ -18811,7 +18838,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>951</v>
       </c>
@@ -18846,7 +18873,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>954</v>
       </c>
@@ -18884,7 +18911,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>956</v>
       </c>
@@ -18925,7 +18952,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>958</v>
       </c>
@@ -18960,7 +18987,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>960</v>
       </c>
@@ -18998,7 +19025,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>961</v>
       </c>
@@ -19036,7 +19063,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>963</v>
       </c>
@@ -19074,7 +19101,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>965</v>
       </c>
@@ -19109,7 +19136,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>969</v>
       </c>
@@ -19147,7 +19174,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>970</v>
       </c>
@@ -19185,7 +19212,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>971</v>
       </c>
@@ -19223,7 +19250,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>972</v>
       </c>
@@ -19261,7 +19288,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>977</v>
       </c>
@@ -19299,7 +19326,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>978</v>
       </c>
@@ -19337,7 +19364,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>979</v>
       </c>
@@ -19375,7 +19402,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>980</v>
       </c>
@@ -19410,7 +19437,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>981</v>
       </c>
@@ -19445,7 +19472,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>982</v>
       </c>
@@ -19480,7 +19507,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>987</v>
       </c>
@@ -19515,7 +19542,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>990</v>
       </c>
@@ -19550,7 +19577,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>992</v>
       </c>
@@ -19588,7 +19615,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>993</v>
       </c>
@@ -19626,7 +19653,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>998</v>
       </c>
@@ -19664,7 +19691,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>999</v>
       </c>
@@ -19702,7 +19729,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1006</v>
       </c>
@@ -19743,7 +19770,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1007</v>
       </c>
@@ -19784,7 +19811,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1009</v>
       </c>
@@ -19825,7 +19852,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1010</v>
       </c>
@@ -19866,7 +19893,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1011</v>
       </c>
@@ -19907,7 +19934,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1012</v>
       </c>
@@ -19948,7 +19975,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1013</v>
       </c>
@@ -19989,7 +20016,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1014</v>
       </c>
@@ -20030,7 +20057,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1015</v>
       </c>
@@ -20071,7 +20098,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1016</v>
       </c>
@@ -20112,7 +20139,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1017</v>
       </c>
@@ -20153,7 +20180,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1018</v>
       </c>
@@ -20194,7 +20221,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1019</v>
       </c>
@@ -20235,7 +20262,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1021</v>
       </c>
@@ -20273,7 +20300,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1022</v>
       </c>
@@ -20311,7 +20338,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1023</v>
       </c>
@@ -20349,7 +20376,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1024</v>
       </c>
@@ -20387,7 +20414,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1025</v>
       </c>
@@ -20425,7 +20452,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1026</v>
       </c>
@@ -20463,7 +20490,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1027</v>
       </c>
@@ -20501,7 +20528,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1028</v>
       </c>
@@ -20539,7 +20566,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1029</v>
       </c>
@@ -20577,7 +20604,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1039</v>
       </c>
@@ -20618,7 +20645,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1047</v>
       </c>
@@ -20659,7 +20686,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1048</v>
       </c>
@@ -20700,7 +20727,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1049</v>
       </c>
@@ -20741,7 +20768,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>1051</v>
       </c>
@@ -20779,7 +20806,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1052</v>
       </c>
@@ -20817,7 +20844,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1053</v>
       </c>
@@ -20855,7 +20882,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1054</v>
       </c>
@@ -20893,7 +20920,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1055</v>
       </c>
@@ -20931,7 +20958,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1060</v>
       </c>
@@ -20969,7 +20996,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1061</v>
       </c>
@@ -21007,7 +21034,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1064</v>
       </c>
@@ -21045,7 +21072,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1066</v>
       </c>
@@ -21083,7 +21110,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1067</v>
       </c>
@@ -21121,7 +21148,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1069</v>
       </c>
@@ -21159,7 +21186,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1071</v>
       </c>
@@ -21197,7 +21224,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1072</v>
       </c>
@@ -21235,7 +21262,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1076</v>
       </c>
@@ -21273,7 +21300,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1075</v>
       </c>
@@ -21311,7 +21338,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1079</v>
       </c>
@@ -21352,7 +21379,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1081</v>
       </c>
@@ -21390,7 +21417,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1085</v>
       </c>
@@ -21428,7 +21455,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>460</v>
       </c>
@@ -21469,7 +21496,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>464</v>
       </c>
@@ -21510,7 +21537,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>465</v>
       </c>
@@ -21551,7 +21578,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>476</v>
       </c>
@@ -21592,7 +21619,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="433" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>467</v>
       </c>
@@ -21636,7 +21663,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="434" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>468</v>
       </c>
@@ -21680,7 +21707,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="435" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>469</v>
       </c>
@@ -21724,7 +21751,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="436" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>470</v>
       </c>
@@ -21768,7 +21795,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="437" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>471</v>
       </c>
@@ -21812,7 +21839,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="438" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>472</v>
       </c>
@@ -21856,7 +21883,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="439" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>851</v>
       </c>
@@ -21894,7 +21921,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="440" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>852</v>
       </c>
@@ -21935,7 +21962,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="441" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>854</v>
       </c>
@@ -21976,7 +22003,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="442" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>713</v>
       </c>
@@ -22017,7 +22044,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="443" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1092</v>
       </c>
@@ -22055,7 +22082,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="444" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1093</v>
       </c>
@@ -22093,7 +22120,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="445" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1094</v>
       </c>
@@ -22131,7 +22158,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="446" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1102</v>
       </c>
@@ -22166,7 +22193,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="447" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1103</v>
       </c>
@@ -22201,7 +22228,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="448" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1105</v>
       </c>
@@ -22233,7 +22260,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1106</v>
       </c>
@@ -22268,7 +22295,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1109</v>
       </c>
@@ -22303,7 +22330,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1111</v>
       </c>
@@ -22338,7 +22365,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1116</v>
       </c>
@@ -22373,7 +22400,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1115</v>
       </c>
@@ -22408,7 +22435,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1114</v>
       </c>
@@ -22443,7 +22470,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1117</v>
       </c>
@@ -22481,7 +22508,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1123</v>
       </c>
@@ -22519,7 +22546,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1127</v>
       </c>
@@ -22529,10 +22556,10 @@
       <c r="C457">
         <v>80</v>
       </c>
-      <c r="H457" s="21">
+      <c r="H457">
         <v>34.844999999999999</v>
       </c>
-      <c r="I457" s="21">
+      <c r="I457">
         <v>-22.184699999999999</v>
       </c>
       <c r="K457" t="s">
@@ -22557,7 +22584,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1128</v>
       </c>
@@ -22567,10 +22594,10 @@
       <c r="C458">
         <v>70</v>
       </c>
-      <c r="H458" s="21">
+      <c r="H458">
         <v>34.844999999999999</v>
       </c>
-      <c r="I458" s="21">
+      <c r="I458">
         <v>-22.184699999999999</v>
       </c>
       <c r="K458" t="s">
@@ -22595,7 +22622,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1129</v>
       </c>
@@ -22605,10 +22632,10 @@
       <c r="C459">
         <v>70</v>
       </c>
-      <c r="H459" s="21">
+      <c r="H459">
         <v>34.844999999999999</v>
       </c>
-      <c r="I459" s="21">
+      <c r="I459">
         <v>-22.184699999999999</v>
       </c>
       <c r="K459" t="s">
@@ -22633,7 +22660,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1130</v>
       </c>
@@ -22643,10 +22670,10 @@
       <c r="C460">
         <v>70</v>
       </c>
-      <c r="H460" s="21">
+      <c r="H460">
         <v>34.844999999999999</v>
       </c>
-      <c r="I460" s="21">
+      <c r="I460">
         <v>-22.184699999999999</v>
       </c>
       <c r="K460" t="s">
@@ -22671,7 +22698,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1131</v>
       </c>
@@ -22681,10 +22708,10 @@
       <c r="C461">
         <v>70</v>
       </c>
-      <c r="H461" s="21">
+      <c r="H461">
         <v>34.844999999999999</v>
       </c>
-      <c r="I461" s="21">
+      <c r="I461">
         <v>-22.184699999999999</v>
       </c>
       <c r="K461" t="s">
@@ -22709,7 +22736,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1132</v>
       </c>
@@ -22719,10 +22746,10 @@
       <c r="C462">
         <v>70</v>
       </c>
-      <c r="H462" s="21">
+      <c r="H462">
         <v>34.844999999999999</v>
       </c>
-      <c r="I462" s="21">
+      <c r="I462">
         <v>-22.184699999999999</v>
       </c>
       <c r="K462" t="s">
@@ -22747,7 +22774,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1133</v>
       </c>
@@ -22757,10 +22784,10 @@
       <c r="C463">
         <v>70</v>
       </c>
-      <c r="H463" s="21">
+      <c r="H463">
         <v>34.844999999999999</v>
       </c>
-      <c r="I463" s="21">
+      <c r="I463">
         <v>-22.184699999999999</v>
       </c>
       <c r="K463" t="s">
@@ -22786,7 +22813,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U438" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}"/>
+  <autoFilter ref="A1:U463" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="Kansanshi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="S2" r:id="rId1" xr:uid="{755983A6-3859-4B38-A82D-53653C69B6F4}"/>
     <hyperlink ref="S3:S8" r:id="rId2" display="https://www.cambridge.org/core/journals/antiquity/article/transition-to-farming-in-eastern-africa-new-faunal-and-dating-evidence-from-wadh-lango-and-usenge-kenya/6349026A5CED7E35C0D7EC4BBF2EFB38  " xr:uid="{26809F61-504A-462D-ADCB-73F893FCD302}"/>
@@ -23168,6 +23201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U487"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -23237,7 +23271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -23287,7 +23321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -23337,7 +23371,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -23387,7 +23421,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -23437,7 +23471,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -23487,7 +23521,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -23537,7 +23571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -23587,7 +23621,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -23631,7 +23665,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>58</v>
       </c>
@@ -23679,7 +23713,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -23720,7 +23754,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -23761,7 +23795,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
@@ -23809,7 +23843,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -23850,7 +23884,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -23894,7 +23928,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -23938,7 +23972,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>80</v>
       </c>
@@ -23979,7 +24013,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -24020,7 +24054,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -24061,7 +24095,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -24102,7 +24136,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -24146,7 +24180,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -24187,7 +24221,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>103</v>
       </c>
@@ -24228,7 +24262,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>107</v>
       </c>
@@ -24274,7 +24308,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>108</v>
       </c>
@@ -24320,7 +24354,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>109</v>
       </c>
@@ -24366,7 +24400,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>110</v>
       </c>
@@ -24412,7 +24446,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>114</v>
       </c>
@@ -24453,7 +24487,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -24491,7 +24525,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -24529,7 +24563,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -24570,7 +24604,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -24611,7 +24645,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -24649,7 +24683,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -24687,7 +24721,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>129</v>
       </c>
@@ -24725,7 +24759,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -24766,7 +24800,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -24807,7 +24841,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>134</v>
       </c>
@@ -24848,7 +24882,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>135</v>
       </c>
@@ -24889,7 +24923,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>136</v>
       </c>
@@ -24923,7 +24957,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>140</v>
       </c>
@@ -24957,7 +24991,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -24991,7 +25025,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>154</v>
       </c>
@@ -25029,7 +25063,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>386</v>
       </c>
@@ -25070,7 +25104,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>159</v>
       </c>
@@ -25111,7 +25145,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>163</v>
       </c>
@@ -25155,7 +25189,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -25196,7 +25230,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>227</v>
       </c>
@@ -25237,7 +25271,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>172</v>
       </c>
@@ -25278,7 +25312,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>177</v>
       </c>
@@ -25319,7 +25353,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>181</v>
       </c>
@@ -25360,7 +25394,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>183</v>
       </c>
@@ -25404,7 +25438,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>186</v>
       </c>
@@ -25448,7 +25482,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>190</v>
       </c>
@@ -25486,7 +25520,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>194</v>
       </c>
@@ -25527,7 +25561,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>195</v>
       </c>
@@ -25568,7 +25602,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>198</v>
       </c>
@@ -25616,7 +25650,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>205</v>
       </c>
@@ -25657,7 +25691,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>211</v>
       </c>
@@ -25698,7 +25732,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>200</v>
       </c>
@@ -25739,7 +25773,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>201</v>
       </c>
@@ -25777,7 +25811,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>202</v>
       </c>
@@ -25815,7 +25849,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>203</v>
       </c>
@@ -25853,7 +25887,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>209</v>
       </c>
@@ -25903,7 +25937,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>210</v>
       </c>
@@ -25951,7 +25985,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>215</v>
       </c>
@@ -25989,7 +26023,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>216</v>
       </c>
@@ -26027,7 +26061,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>217</v>
       </c>
@@ -26068,7 +26102,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>223</v>
       </c>
@@ -26109,7 +26143,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>224</v>
       </c>
@@ -26150,7 +26184,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>343</v>
       </c>
@@ -26194,7 +26228,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>226</v>
       </c>
@@ -26245,7 +26279,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>234</v>
       </c>
@@ -26294,7 +26328,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>230</v>
       </c>
@@ -26343,7 +26377,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>231</v>
       </c>
@@ -26392,7 +26426,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>242</v>
       </c>
@@ -26433,7 +26467,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>244</v>
       </c>
@@ -26472,7 +26506,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>245</v>
       </c>
@@ -26522,10 +26556,10 @@
         <v>90</v>
       </c>
       <c r="H79">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I79">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K79" t="s">
         <v>38</v>
@@ -26560,10 +26594,10 @@
         <v>85</v>
       </c>
       <c r="H80">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I80">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K80" t="s">
         <v>38</v>
@@ -26598,10 +26632,10 @@
         <v>85</v>
       </c>
       <c r="H81">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I81">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K81" t="s">
         <v>38</v>
@@ -26636,10 +26670,10 @@
         <v>60</v>
       </c>
       <c r="H82">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I82">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K82" t="s">
         <v>38</v>
@@ -26674,10 +26708,10 @@
         <v>75</v>
       </c>
       <c r="H83">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I83">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K83" t="s">
         <v>131</v>
@@ -26712,10 +26746,10 @@
         <v>75</v>
       </c>
       <c r="H84">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I84">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K84" t="s">
         <v>131</v>
@@ -26750,10 +26784,10 @@
         <v>80</v>
       </c>
       <c r="H85">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I85">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K85" t="s">
         <v>131</v>
@@ -26788,10 +26822,10 @@
         <v>80</v>
       </c>
       <c r="H86">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="I86">
-        <v>-11.67</v>
+        <v>-12.2</v>
       </c>
       <c r="K86" t="s">
         <v>131</v>
@@ -26815,7 +26849,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -26853,7 +26887,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>257</v>
       </c>
@@ -26891,7 +26925,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>258</v>
       </c>
@@ -26929,7 +26963,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>260</v>
       </c>
@@ -26967,7 +27001,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>263</v>
       </c>
@@ -27008,7 +27042,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>264</v>
       </c>
@@ -27049,7 +27083,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>265</v>
       </c>
@@ -27090,7 +27124,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>268</v>
       </c>
@@ -27131,7 +27165,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>269</v>
       </c>
@@ -27172,7 +27206,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>270</v>
       </c>
@@ -27213,7 +27247,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>271</v>
       </c>
@@ -27251,7 +27285,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>272</v>
       </c>
@@ -27289,7 +27323,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>273</v>
       </c>
@@ -27330,7 +27364,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>274</v>
       </c>
@@ -27371,7 +27405,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>278</v>
       </c>
@@ -27412,7 +27446,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>281</v>
       </c>
@@ -27450,7 +27484,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>282</v>
       </c>
@@ -27488,7 +27522,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>287</v>
       </c>
@@ -27526,7 +27560,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>283</v>
       </c>
@@ -27564,7 +27598,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>284</v>
       </c>
@@ -27602,7 +27636,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>285</v>
       </c>
@@ -27640,7 +27674,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>286</v>
       </c>
@@ -27678,7 +27712,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>287</v>
       </c>
@@ -27716,7 +27750,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>288</v>
       </c>
@@ -27760,7 +27794,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>289</v>
       </c>
@@ -27804,7 +27838,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>292</v>
       </c>
@@ -27848,7 +27882,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>293</v>
       </c>
@@ -27886,7 +27920,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>295</v>
       </c>
@@ -27924,7 +27958,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>296</v>
       </c>
@@ -27962,7 +27996,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>302</v>
       </c>
@@ -28000,7 +28034,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>303</v>
       </c>
@@ -28041,7 +28075,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>304</v>
       </c>
@@ -28080,7 +28114,7 @@
       </c>
       <c r="T118" s="12"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>307</v>
       </c>
@@ -28121,7 +28155,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>308</v>
       </c>
@@ -28159,7 +28193,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>309</v>
       </c>
@@ -28200,7 +28234,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>310</v>
       </c>
@@ -28241,7 +28275,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>319</v>
       </c>
@@ -28285,7 +28319,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>320</v>
       </c>
@@ -28326,7 +28360,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>326</v>
       </c>
@@ -28376,7 +28410,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>332</v>
       </c>
@@ -28414,7 +28448,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>333</v>
       </c>
@@ -28452,7 +28486,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>334</v>
       </c>
@@ -28490,7 +28524,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>346</v>
       </c>
@@ -28534,7 +28568,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>347</v>
       </c>
@@ -28578,7 +28612,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>348</v>
       </c>
@@ -28622,7 +28656,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>349</v>
       </c>
@@ -28666,7 +28700,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>357</v>
       </c>
@@ -28707,7 +28741,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>358</v>
       </c>
@@ -28748,7 +28782,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>361</v>
       </c>
@@ -28789,7 +28823,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>363</v>
       </c>
@@ -28830,7 +28864,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>367</v>
       </c>
@@ -28871,7 +28905,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>368</v>
       </c>
@@ -28912,7 +28946,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>371</v>
       </c>
@@ -28960,7 +28994,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>372</v>
       </c>
@@ -29001,7 +29035,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="16" t="s">
         <v>373</v>
       </c>
@@ -29049,7 +29083,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>374</v>
       </c>
@@ -29090,7 +29124,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="16" t="s">
         <v>375</v>
       </c>
@@ -29138,7 +29172,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>376</v>
       </c>
@@ -29179,7 +29213,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="16" t="s">
         <v>377</v>
       </c>
@@ -29227,7 +29261,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>378</v>
       </c>
@@ -29268,7 +29302,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>381</v>
       </c>
@@ -29306,7 +29340,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>382</v>
       </c>
@@ -29344,7 +29378,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>383</v>
       </c>
@@ -29382,7 +29416,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>384</v>
       </c>
@@ -29420,7 +29454,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>392</v>
       </c>
@@ -29461,7 +29495,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>395</v>
       </c>
@@ -29502,7 +29536,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>406</v>
       </c>
@@ -29543,7 +29577,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>407</v>
       </c>
@@ -29584,7 +29618,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>408</v>
       </c>
@@ -29625,7 +29659,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>409</v>
       </c>
@@ -29666,7 +29700,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>410</v>
       </c>
@@ -29707,7 +29741,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>411</v>
       </c>
@@ -29748,7 +29782,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>412</v>
       </c>
@@ -29789,7 +29823,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>413</v>
       </c>
@@ -29830,7 +29864,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>419</v>
       </c>
@@ -29871,7 +29905,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>420</v>
       </c>
@@ -29912,7 +29946,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>421</v>
       </c>
@@ -29953,7 +29987,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>422</v>
       </c>
@@ -29994,7 +30028,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>423</v>
       </c>
@@ -30035,7 +30069,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>424</v>
       </c>
@@ -30076,7 +30110,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>425</v>
       </c>
@@ -30117,7 +30151,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>430</v>
       </c>
@@ -30161,7 +30195,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>432</v>
       </c>
@@ -30202,7 +30236,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>440</v>
       </c>
@@ -30246,7 +30280,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>443</v>
       </c>
@@ -30290,7 +30324,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>448</v>
       </c>
@@ -30334,7 +30368,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>681</v>
       </c>
@@ -30378,7 +30412,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>452</v>
       </c>
@@ -30419,7 +30453,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>455</v>
       </c>
@@ -30460,7 +30494,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>460</v>
       </c>
@@ -30501,7 +30535,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>464</v>
       </c>
@@ -30542,7 +30576,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>465</v>
       </c>
@@ -30583,7 +30617,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>476</v>
       </c>
@@ -30624,7 +30658,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>467</v>
       </c>
@@ -30668,7 +30702,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>468</v>
       </c>
@@ -30712,7 +30746,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>469</v>
       </c>
@@ -30756,7 +30790,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>470</v>
       </c>
@@ -30800,7 +30834,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>471</v>
       </c>
@@ -30844,7 +30878,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>472</v>
       </c>
@@ -30888,7 +30922,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>487</v>
       </c>
@@ -30929,7 +30963,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>489</v>
       </c>
@@ -30973,7 +31007,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>491</v>
       </c>
@@ -31017,7 +31051,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>492</v>
       </c>
@@ -31061,7 +31095,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="14" t="s">
         <v>493</v>
       </c>
@@ -31105,7 +31139,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>494</v>
       </c>
@@ -31149,7 +31183,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>495</v>
       </c>
@@ -31193,7 +31227,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>496</v>
       </c>
@@ -31237,7 +31271,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>497</v>
       </c>
@@ -31281,7 +31315,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>498</v>
       </c>
@@ -31325,7 +31359,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>499</v>
       </c>
@@ -31369,7 +31403,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>500</v>
       </c>
@@ -31413,7 +31447,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>501</v>
       </c>
@@ -31457,7 +31491,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>515</v>
       </c>
@@ -31501,7 +31535,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>516</v>
       </c>
@@ -31545,7 +31579,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>517</v>
       </c>
@@ -31589,7 +31623,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>518</v>
       </c>
@@ -31633,7 +31667,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>519</v>
       </c>
@@ -31677,7 +31711,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>540</v>
       </c>
@@ -31721,7 +31755,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>541</v>
       </c>
@@ -31765,7 +31799,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>542</v>
       </c>
@@ -31809,7 +31843,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>548</v>
       </c>
@@ -31850,7 +31884,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>551</v>
       </c>
@@ -31891,7 +31925,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>561</v>
       </c>
@@ -31932,7 +31966,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>552</v>
       </c>
@@ -31973,7 +32007,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>554</v>
       </c>
@@ -32017,7 +32051,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>557</v>
       </c>
@@ -32058,7 +32092,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>559</v>
       </c>
@@ -32099,7 +32133,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>563</v>
       </c>
@@ -32140,7 +32174,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>589</v>
       </c>
@@ -32184,7 +32218,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>590</v>
       </c>
@@ -32225,7 +32259,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>572</v>
       </c>
@@ -32263,7 +32297,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>577</v>
       </c>
@@ -32301,7 +32335,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>579</v>
       </c>
@@ -32339,7 +32373,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>580</v>
       </c>
@@ -32377,7 +32411,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>584</v>
       </c>
@@ -32415,7 +32449,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>585</v>
       </c>
@@ -32453,7 +32487,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>586</v>
       </c>
@@ -32491,7 +32525,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>587</v>
       </c>
@@ -32529,7 +32563,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>591</v>
       </c>
@@ -32570,7 +32604,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>592</v>
       </c>
@@ -32611,7 +32645,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>593</v>
       </c>
@@ -32652,7 +32686,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>594</v>
       </c>
@@ -32693,7 +32727,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>595</v>
       </c>
@@ -32734,7 +32768,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>596</v>
       </c>
@@ -32775,7 +32809,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>601</v>
       </c>
@@ -32813,7 +32847,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>602</v>
       </c>
@@ -32851,7 +32885,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>603</v>
       </c>
@@ -32889,7 +32923,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>604</v>
       </c>
@@ -32927,7 +32961,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>609</v>
       </c>
@@ -32968,7 +33002,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>608</v>
       </c>
@@ -33006,7 +33040,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>607</v>
       </c>
@@ -33044,7 +33078,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>610</v>
       </c>
@@ -33082,7 +33116,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>611</v>
       </c>
@@ -33120,7 +33154,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>612</v>
       </c>
@@ -33158,7 +33192,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>613</v>
       </c>
@@ -33196,7 +33230,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>616</v>
       </c>
@@ -33234,7 +33268,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>618</v>
       </c>
@@ -33272,7 +33306,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>619</v>
       </c>
@@ -33310,7 +33344,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>621</v>
       </c>
@@ -33348,7 +33382,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>620</v>
       </c>
@@ -33386,7 +33420,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>623</v>
       </c>
@@ -33421,7 +33455,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>624</v>
       </c>
@@ -33462,7 +33496,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>629</v>
       </c>
@@ -33500,7 +33534,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>630</v>
       </c>
@@ -33538,7 +33572,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>634</v>
       </c>
@@ -33579,7 +33613,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>635</v>
       </c>
@@ -33620,7 +33654,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>636</v>
       </c>
@@ -33658,7 +33692,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>637</v>
       </c>
@@ -33696,7 +33730,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>337</v>
       </c>
@@ -33734,7 +33768,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>638</v>
       </c>
@@ -33772,7 +33806,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>639</v>
       </c>
@@ -33810,7 +33844,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>640</v>
       </c>
@@ -33848,7 +33882,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>647</v>
       </c>
@@ -33892,7 +33926,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>653</v>
       </c>
@@ -33930,7 +33964,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="15" t="s">
         <v>654</v>
       </c>
@@ -33968,7 +34002,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>662</v>
       </c>
@@ -34006,7 +34040,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>663</v>
       </c>
@@ -34044,7 +34078,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>664</v>
       </c>
@@ -34082,7 +34116,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>665</v>
       </c>
@@ -34120,7 +34154,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>666</v>
       </c>
@@ -34158,7 +34192,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>669</v>
       </c>
@@ -34202,7 +34236,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>673</v>
       </c>
@@ -34243,7 +34277,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>674</v>
       </c>
@@ -34284,7 +34318,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>675</v>
       </c>
@@ -34322,7 +34356,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>676</v>
       </c>
@@ -34360,7 +34394,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>682</v>
       </c>
@@ -34398,7 +34432,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>683</v>
       </c>
@@ -34439,7 +34473,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>684</v>
       </c>
@@ -34477,7 +34511,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>685</v>
       </c>
@@ -34515,7 +34549,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>696</v>
       </c>
@@ -34556,7 +34590,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>693</v>
       </c>
@@ -34597,7 +34631,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>701</v>
       </c>
@@ -34638,7 +34672,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>702</v>
       </c>
@@ -34679,7 +34713,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>703</v>
       </c>
@@ -34720,7 +34754,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>706</v>
       </c>
@@ -34761,7 +34795,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>707</v>
       </c>
@@ -34799,7 +34833,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>708</v>
       </c>
@@ -34837,7 +34871,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>709</v>
       </c>
@@ -34872,7 +34906,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>710</v>
       </c>
@@ -34907,7 +34941,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>711</v>
       </c>
@@ -34942,7 +34976,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>712</v>
       </c>
@@ -34977,7 +35011,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>713</v>
       </c>
@@ -35018,7 +35052,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>716</v>
       </c>
@@ -35059,7 +35093,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>717</v>
       </c>
@@ -35103,7 +35137,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>721</v>
       </c>
@@ -35147,7 +35181,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>722</v>
       </c>
@@ -35191,7 +35225,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>723</v>
       </c>
@@ -35235,7 +35269,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>724</v>
       </c>
@@ -35279,7 +35313,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>727</v>
       </c>
@@ -35317,7 +35351,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>729</v>
       </c>
@@ -35358,7 +35392,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>730</v>
       </c>
@@ -35399,7 +35433,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>734</v>
       </c>
@@ -35443,7 +35477,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>738</v>
       </c>
@@ -35487,7 +35521,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>739</v>
       </c>
@@ -35531,7 +35565,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>740</v>
       </c>
@@ -35572,7 +35606,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>741</v>
       </c>
@@ -35613,7 +35647,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>742</v>
       </c>
@@ -35654,7 +35688,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>743</v>
       </c>
@@ -35695,7 +35729,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>747</v>
       </c>
@@ -35733,7 +35767,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>750</v>
       </c>
@@ -35774,7 +35808,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>753</v>
       </c>
@@ -35818,7 +35852,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
         <v>757</v>
       </c>
@@ -35856,7 +35890,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>757</v>
       </c>
@@ -35894,7 +35928,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="10" t="s">
         <v>757</v>
       </c>
@@ -35932,7 +35966,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
         <v>757</v>
       </c>
@@ -35970,7 +36004,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="10" t="s">
         <v>757</v>
       </c>
@@ -36008,7 +36042,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>766</v>
       </c>
@@ -36046,7 +36080,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>767</v>
       </c>
@@ -36084,7 +36118,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>768</v>
       </c>
@@ -36122,7 +36156,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>770</v>
       </c>
@@ -36160,7 +36194,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>771</v>
       </c>
@@ -36198,7 +36232,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>778</v>
       </c>
@@ -36239,7 +36273,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>784</v>
       </c>
@@ -36280,7 +36314,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>785</v>
       </c>
@@ -36321,7 +36355,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>790</v>
       </c>
@@ -36359,7 +36393,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>791</v>
       </c>
@@ -36397,7 +36431,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>795</v>
       </c>
@@ -36438,7 +36472,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>798</v>
       </c>
@@ -36476,7 +36510,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>799</v>
       </c>
@@ -36517,7 +36551,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>800</v>
       </c>
@@ -36558,7 +36592,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>803</v>
       </c>
@@ -36599,7 +36633,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>806</v>
       </c>
@@ -36637,7 +36671,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>807</v>
       </c>
@@ -36678,7 +36712,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>808</v>
       </c>
@@ -36719,7 +36753,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>809</v>
       </c>
@@ -36757,7 +36791,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>816</v>
       </c>
@@ -36798,7 +36832,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>817</v>
       </c>
@@ -36839,7 +36873,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>822</v>
       </c>
@@ -36877,7 +36911,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>823</v>
       </c>
@@ -36915,7 +36949,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>824</v>
       </c>
@@ -36953,7 +36987,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>825</v>
       </c>
@@ -36991,7 +37025,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>826</v>
       </c>
@@ -37029,7 +37063,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>835</v>
       </c>
@@ -37070,7 +37104,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>836</v>
       </c>
@@ -37108,7 +37142,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>837</v>
       </c>
@@ -37146,7 +37180,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>841</v>
       </c>
@@ -37187,7 +37221,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>842</v>
       </c>
@@ -37228,7 +37262,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>843</v>
       </c>
@@ -37269,7 +37303,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>844</v>
       </c>
@@ -37310,7 +37344,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>845</v>
       </c>
@@ -37351,7 +37385,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>851</v>
       </c>
@@ -37389,7 +37423,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>852</v>
       </c>
@@ -37430,7 +37464,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>854</v>
       </c>
@@ -37471,7 +37505,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>860</v>
       </c>
@@ -37506,7 +37540,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>861</v>
       </c>
@@ -37541,7 +37575,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>862</v>
       </c>
@@ -37576,7 +37610,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>863</v>
       </c>
@@ -37611,7 +37645,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>864</v>
       </c>
@@ -37649,7 +37683,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>865</v>
       </c>
@@ -37684,7 +37718,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>866</v>
       </c>
@@ -37722,7 +37756,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>867</v>
       </c>
@@ -37760,7 +37794,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>868</v>
       </c>
@@ -37798,7 +37832,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>907</v>
       </c>
@@ -37836,7 +37870,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>869</v>
       </c>
@@ -37874,7 +37908,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>870</v>
       </c>
@@ -37912,7 +37946,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>872</v>
       </c>
@@ -37956,7 +37990,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>874</v>
       </c>
@@ -37997,7 +38031,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>875</v>
       </c>
@@ -38038,7 +38072,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>876</v>
       </c>
@@ -38082,7 +38116,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>877</v>
       </c>
@@ -38123,7 +38157,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>878</v>
       </c>
@@ -38164,7 +38198,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>879</v>
       </c>
@@ -38205,7 +38239,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>883</v>
       </c>
@@ -38249,7 +38283,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>888</v>
       </c>
@@ -38293,7 +38327,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>895</v>
       </c>
@@ -38337,7 +38371,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>896</v>
       </c>
@@ -38378,7 +38412,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>900</v>
       </c>
@@ -38419,7 +38453,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>903</v>
       </c>
@@ -38457,7 +38491,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>904</v>
       </c>
@@ -38498,7 +38532,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>910</v>
       </c>
@@ -38539,7 +38573,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>911</v>
       </c>
@@ -38577,7 +38611,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>912</v>
       </c>
@@ -38615,7 +38649,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>915</v>
       </c>
@@ -38653,7 +38687,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>916</v>
       </c>
@@ -38694,7 +38728,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="16" t="s">
         <v>917</v>
       </c>
@@ -38740,7 +38774,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="16" t="s">
         <v>918</v>
       </c>
@@ -38788,7 +38822,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>924</v>
       </c>
@@ -38826,7 +38860,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>925</v>
       </c>
@@ -38864,7 +38898,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>926</v>
       </c>
@@ -38905,7 +38939,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>927</v>
       </c>
@@ -38943,7 +38977,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>929</v>
       </c>
@@ -38984,7 +39018,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>934</v>
       </c>
@@ -39019,7 +39053,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>936</v>
       </c>
@@ -39054,7 +39088,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>937</v>
       </c>
@@ -39089,7 +39123,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>939</v>
       </c>
@@ -39127,7 +39161,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>944</v>
       </c>
@@ -39162,7 +39196,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>945</v>
       </c>
@@ -39200,7 +39234,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>946</v>
       </c>
@@ -39238,7 +39272,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>947</v>
       </c>
@@ -39276,7 +39310,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>948</v>
       </c>
@@ -39314,7 +39348,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>949</v>
       </c>
@@ -39352,7 +39386,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>951</v>
       </c>
@@ -39387,7 +39421,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>954</v>
       </c>
@@ -39425,7 +39459,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>956</v>
       </c>
@@ -39466,7 +39500,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>958</v>
       </c>
@@ -39501,7 +39535,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>960</v>
       </c>
@@ -39539,7 +39573,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>961</v>
       </c>
@@ -39577,7 +39611,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>963</v>
       </c>
@@ -39615,7 +39649,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>965</v>
       </c>
@@ -39650,7 +39684,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>969</v>
       </c>
@@ -39688,7 +39722,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>970</v>
       </c>
@@ -39726,7 +39760,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>971</v>
       </c>
@@ -39764,7 +39798,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>972</v>
       </c>
@@ -39802,7 +39836,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>977</v>
       </c>
@@ -39840,7 +39874,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>978</v>
       </c>
@@ -39878,7 +39912,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>979</v>
       </c>
@@ -39916,7 +39950,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>980</v>
       </c>
@@ -39951,7 +39985,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>981</v>
       </c>
@@ -39986,7 +40020,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>982</v>
       </c>
@@ -40021,7 +40055,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>987</v>
       </c>
@@ -40056,7 +40090,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>990</v>
       </c>
@@ -40091,7 +40125,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>992</v>
       </c>
@@ -40129,7 +40163,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>993</v>
       </c>
@@ -40167,7 +40201,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>998</v>
       </c>
@@ -40205,7 +40239,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>999</v>
       </c>
@@ -40243,7 +40277,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1006</v>
       </c>
@@ -40284,7 +40318,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1007</v>
       </c>
@@ -40325,7 +40359,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
         <v>1008</v>
       </c>
@@ -40373,7 +40407,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1009</v>
       </c>
@@ -40414,7 +40448,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1010</v>
       </c>
@@ -40455,7 +40489,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1011</v>
       </c>
@@ -40496,7 +40530,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1012</v>
       </c>
@@ -40537,7 +40571,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1013</v>
       </c>
@@ -40578,7 +40612,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1014</v>
       </c>
@@ -40619,7 +40653,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1015</v>
       </c>
@@ -40660,7 +40694,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1016</v>
       </c>
@@ -40701,7 +40735,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1017</v>
       </c>
@@ -40742,7 +40776,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1018</v>
       </c>
@@ -40783,7 +40817,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1019</v>
       </c>
@@ -40824,7 +40858,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1021</v>
       </c>
@@ -40862,7 +40896,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1022</v>
       </c>
@@ -40900,7 +40934,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="438" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1023</v>
       </c>
@@ -40938,7 +40972,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="439" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1024</v>
       </c>
@@ -40976,7 +41010,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="440" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1025</v>
       </c>
@@ -41014,7 +41048,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1026</v>
       </c>
@@ -41052,7 +41086,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1027</v>
       </c>
@@ -41090,7 +41124,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1028</v>
       </c>
@@ -41128,7 +41162,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1029</v>
       </c>
@@ -41166,7 +41200,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1039</v>
       </c>
@@ -41207,7 +41241,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1047</v>
       </c>
@@ -41248,7 +41282,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1048</v>
       </c>
@@ -41289,7 +41323,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1049</v>
       </c>
@@ -41330,7 +41364,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1051</v>
       </c>
@@ -41368,7 +41402,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1052</v>
       </c>
@@ -41406,7 +41440,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1053</v>
       </c>
@@ -41444,7 +41478,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1054</v>
       </c>
@@ -41482,7 +41516,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1055</v>
       </c>
@@ -41520,7 +41554,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1060</v>
       </c>
@@ -41558,7 +41592,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1061</v>
       </c>
@@ -41596,7 +41630,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1064</v>
       </c>
@@ -41634,7 +41668,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1066</v>
       </c>
@@ -41672,7 +41706,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1067</v>
       </c>
@@ -41710,7 +41744,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1069</v>
       </c>
@@ -41748,7 +41782,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1071</v>
       </c>
@@ -41786,7 +41820,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1072</v>
       </c>
@@ -41824,7 +41858,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1076</v>
       </c>
@@ -41862,7 +41896,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1075</v>
       </c>
@@ -41900,7 +41934,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1079</v>
       </c>
@@ -41941,7 +41975,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1081</v>
       </c>
@@ -41979,7 +42013,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1085</v>
       </c>
@@ -42017,7 +42051,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1092</v>
       </c>
@@ -42055,7 +42089,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1093</v>
       </c>
@@ -42093,7 +42127,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1094</v>
       </c>
@@ -42131,7 +42165,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1102</v>
       </c>
@@ -42166,7 +42200,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1103</v>
       </c>
@@ -42201,7 +42235,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1105</v>
       </c>
@@ -42233,7 +42267,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1106</v>
       </c>
@@ -42268,7 +42302,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1109</v>
       </c>
@@ -42303,7 +42337,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1111</v>
       </c>
@@ -42338,7 +42372,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1116</v>
       </c>
@@ -42373,7 +42407,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1115</v>
       </c>
@@ -42408,7 +42442,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1114</v>
       </c>
@@ -42443,7 +42477,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1117</v>
       </c>
@@ -42481,7 +42515,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1123</v>
       </c>
@@ -42519,7 +42553,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1127</v>
       </c>
@@ -42529,10 +42563,10 @@
       <c r="C481">
         <v>80</v>
       </c>
-      <c r="H481" s="21">
+      <c r="H481">
         <v>34.844999999999999</v>
       </c>
-      <c r="I481" s="21">
+      <c r="I481">
         <v>-22.184699999999999</v>
       </c>
       <c r="K481" t="s">
@@ -42557,7 +42591,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1128</v>
       </c>
@@ -42567,10 +42601,10 @@
       <c r="C482">
         <v>70</v>
       </c>
-      <c r="H482" s="21">
+      <c r="H482">
         <v>34.844999999999999</v>
       </c>
-      <c r="I482" s="21">
+      <c r="I482">
         <v>-22.184699999999999</v>
       </c>
       <c r="K482" t="s">
@@ -42595,7 +42629,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1129</v>
       </c>
@@ -42605,10 +42639,10 @@
       <c r="C483">
         <v>70</v>
       </c>
-      <c r="H483" s="21">
+      <c r="H483">
         <v>34.844999999999999</v>
       </c>
-      <c r="I483" s="21">
+      <c r="I483">
         <v>-22.184699999999999</v>
       </c>
       <c r="K483" t="s">
@@ -42633,7 +42667,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1130</v>
       </c>
@@ -42643,10 +42677,10 @@
       <c r="C484">
         <v>70</v>
       </c>
-      <c r="H484" s="21">
+      <c r="H484">
         <v>34.844999999999999</v>
       </c>
-      <c r="I484" s="21">
+      <c r="I484">
         <v>-22.184699999999999</v>
       </c>
       <c r="K484" t="s">
@@ -42671,7 +42705,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1131</v>
       </c>
@@ -42681,10 +42715,10 @@
       <c r="C485">
         <v>70</v>
       </c>
-      <c r="H485" s="21">
+      <c r="H485">
         <v>34.844999999999999</v>
       </c>
-      <c r="I485" s="21">
+      <c r="I485">
         <v>-22.184699999999999</v>
       </c>
       <c r="K485" t="s">
@@ -42709,7 +42743,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1132</v>
       </c>
@@ -42719,10 +42753,10 @@
       <c r="C486">
         <v>70</v>
       </c>
-      <c r="H486" s="21">
+      <c r="H486">
         <v>34.844999999999999</v>
       </c>
-      <c r="I486" s="21">
+      <c r="I486">
         <v>-22.184699999999999</v>
       </c>
       <c r="K486" t="s">
@@ -42747,7 +42781,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1133</v>
       </c>
@@ -42757,10 +42791,10 @@
       <c r="C487">
         <v>70</v>
       </c>
-      <c r="H487" s="21">
+      <c r="H487">
         <v>34.844999999999999</v>
       </c>
-      <c r="I487" s="21">
+      <c r="I487">
         <v>-22.184699999999999</v>
       </c>
       <c r="K487" t="s">
@@ -42786,7 +42820,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U480" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}"/>
+  <autoFilter ref="A1:U487" xr:uid="{E168D24B-2DCA-4AA5-9768-AE7B822E6C83}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="Kansanshi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="S2" r:id="rId1" xr:uid="{C02C29D8-F2C4-411E-BE0F-C14F29344E0E}"/>
